--- a/LuBan/DataTables/Datas/i18nConsole001.xlsx
+++ b/LuBan/DataTables/Datas/i18nConsole001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="14940" windowHeight="6165" firstSheet="3" activeTab="3"/>
+    <workbookView windowHeight="11580" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="13" state="hidden" r:id="rId1"/>
@@ -1360,10 +1360,10 @@
     <t>Max Coin In Out Record:</t>
   </si>
   <si>
-    <t>投退币记录最大次数:</t>
-  </si>
-  <si>
-    <t>投退幣記錄最大數:</t>
+    <t>投退记录最大次数:</t>
+  </si>
+  <si>
+    <t>投退記錄最大數:</t>
   </si>
   <si>
     <t>CON1zdywcsjl</t>
@@ -2575,10 +2575,10 @@
     <t>Total Bet:</t>
   </si>
   <si>
-    <t>历史总押分:</t>
-  </si>
-  <si>
-    <t>歷史總押分:</t>
+    <t>历史总鼓励值:</t>
+  </si>
+  <si>
+    <t>歷史總鼓勵值:</t>
   </si>
   <si>
     <t>CON1lszyf01</t>
@@ -2659,10 +2659,10 @@
     <t>Total Profit:</t>
   </si>
   <si>
-    <t>总盈利:</t>
-  </si>
-  <si>
-    <t>總盈利:</t>
+    <t>总盈余:</t>
+  </si>
+  <si>
+    <t>總盈餘:</t>
   </si>
   <si>
     <t>CON1zdxxxx</t>
@@ -2770,10 +2770,10 @@
     <t>CON1lszbet02</t>
   </si>
   <si>
-    <t>总押分:</t>
-  </si>
-  <si>
-    <t>總押分:</t>
+    <t>总鼓励值:</t>
+  </si>
+  <si>
+    <t>總鼓勵值:</t>
   </si>
   <si>
     <t>CON1lszwin02</t>
@@ -2923,10 +2923,10 @@
     <t>Coin In-Out History, Page {0} of {1}</t>
   </si>
   <si>
-    <t>投退币历史，页: {0} / {1}</t>
-  </si>
-  <si>
-    <t>投退幣歷史，頁: {0} / {1}</t>
+    <t>投退历史，页: {0} / {1}</t>
+  </si>
+  <si>
+    <t>投退歷史，頁: {0} / {1}</t>
   </si>
   <si>
     <t>_CON1cjls</t>
@@ -2971,10 +2971,10 @@
     <t>COIN</t>
   </si>
   <si>
-    <t>投退币记录</t>
-  </si>
-  <si>
-    <t>投退幣記錄</t>
+    <t>投退记录</t>
+  </si>
+  <si>
+    <t>投退記錄</t>
   </si>
   <si>
     <t>CON1cjljl</t>
@@ -3040,10 +3040,10 @@
     <t>CON1ztz</t>
   </si>
   <si>
-    <t>总投注:</t>
-  </si>
-  <si>
-    <t>總投注:</t>
+    <t>当前鼓励值:</t>
+  </si>
+  <si>
+    <t>當前鼓勵值:</t>
   </si>
   <si>
     <t>CON1zyf</t>
@@ -4219,10 +4219,10 @@
     <t>Set Bet</t>
   </si>
   <si>
-    <t>设置押注</t>
-  </si>
-  <si>
-    <t>設定壓注</t>
+    <t>设置鼓励值</t>
+  </si>
+  <si>
+    <t>設定鼓勵值</t>
   </si>
   <si>
     <t>_CON1jzzdz</t>
@@ -4327,10 +4327,10 @@
     <t>Max Coin In Out Record</t>
   </si>
   <si>
-    <t>投退币记录最大次数</t>
-  </si>
-  <si>
-    <t>投退幣記錄最大次數</t>
+    <t>投退记录最大次数</t>
+  </si>
+  <si>
+    <t>投退記錄最大次數</t>
   </si>
   <si>
     <t>_CON1zdyxjlcs</t>
@@ -4753,10 +4753,10 @@
     <t>The bet value must be between {0} and {1}</t>
   </si>
   <si>
-    <t>押注分数必须在{0}和{1}这间</t>
-  </si>
-  <si>
-    <t>壓注分數必須在{0}和{1}這間</t>
+    <t>鼓励值分数必须在{0}和{1}这间</t>
+  </si>
+  <si>
+    <t>鼓勵值分數必須在{0}和{1}這間</t>
   </si>
   <si>
     <t>_CON1qsrndx</t>
@@ -5086,10 +5086,10 @@
     <t>[Note]: Only retain the most recent {0} In-Out data.</t>
   </si>
   <si>
-    <t>[注意]: 只保留最近的{0}次投退币数据。</t>
-  </si>
-  <si>
-    <t>[注意]：只保留最近的{0}次投退幣數據。</t>
+    <t>[注意]: 只保留最近的{0}次投退数据。</t>
+  </si>
+  <si>
+    <t>[注意]：只保留最近的{0}次投退數據。</t>
   </si>
   <si>
     <t>_CON1jjjrszjm</t>
@@ -5278,10 +5278,10 @@
     <t>The betting list option does not support closing all options.</t>
   </si>
   <si>
-    <t>押注列表选项不支持全部关闭。</t>
-  </si>
-  <si>
-    <t>押注清單選項不支持全部關閉。</t>
+    <t>鼓励值列表选项不支持全部关闭。</t>
+  </si>
+  <si>
+    <t>鼓励值清單選項不支持全部關閉。</t>
   </si>
   <si>
     <t>钱箱-二维码上下分</t>
@@ -5538,7 +5538,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5610,6 +5610,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="NanumGothic"/>
@@ -5620,13 +5628,6 @@
       <color theme="1"/>
       <name val="NanumGothic"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -5652,14 +5653,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -5806,13 +5799,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -5827,7 +5813,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5908,18 +5894,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5939,12 +5913,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6243,13 +6211,16 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6258,145 +6229,141 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6409,12 +6376,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="24" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="24" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6425,22 +6391,22 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6451,6 +6417,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6472,12 +6441,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -6605,8 +6568,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1857375" y="3629025"/>
-          <a:ext cx="1047750" cy="1156335"/>
+          <a:off x="1857375" y="3543300"/>
+          <a:ext cx="1047750" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6649,8 +6612,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5203190" y="3607435"/>
-          <a:ext cx="1129665" cy="1154430"/>
+          <a:off x="5203190" y="3543300"/>
+          <a:ext cx="1129665" cy="989965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6693,8 +6656,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4070985" y="3607435"/>
-          <a:ext cx="1129665" cy="1154430"/>
+          <a:off x="4070985" y="3543300"/>
+          <a:ext cx="1129665" cy="989965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6737,8 +6700,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10983595" y="3714115"/>
-          <a:ext cx="882015" cy="887730"/>
+          <a:off x="10983595" y="3628390"/>
+          <a:ext cx="882015" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6781,8 +6744,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12115165" y="3714115"/>
-          <a:ext cx="882650" cy="887730"/>
+          <a:off x="12115165" y="3628390"/>
+          <a:ext cx="882650" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6825,8 +6788,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6334760" y="3607435"/>
-          <a:ext cx="1130300" cy="1154430"/>
+          <a:off x="6334760" y="3543300"/>
+          <a:ext cx="1130300" cy="989965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6869,8 +6832,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7466965" y="3607435"/>
-          <a:ext cx="1129665" cy="1154430"/>
+          <a:off x="7466965" y="3543300"/>
+          <a:ext cx="1129665" cy="989965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6913,8 +6876,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9851390" y="3714115"/>
-          <a:ext cx="882015" cy="887730"/>
+          <a:off x="9851390" y="3628390"/>
+          <a:ext cx="882015" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6957,8 +6920,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8719185" y="3714115"/>
-          <a:ext cx="882650" cy="887730"/>
+          <a:off x="8719185" y="3628390"/>
+          <a:ext cx="882650" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7001,8 +6964,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2805430" y="3665855"/>
-          <a:ext cx="1403350" cy="1058545"/>
+          <a:off x="2805430" y="3580130"/>
+          <a:ext cx="1403350" cy="915670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7045,8 +7008,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13247370" y="3714115"/>
-          <a:ext cx="882015" cy="887730"/>
+          <a:off x="13247370" y="3628390"/>
+          <a:ext cx="882015" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7089,8 +7052,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14378940" y="3714115"/>
-          <a:ext cx="882650" cy="887730"/>
+          <a:off x="14378940" y="3628390"/>
+          <a:ext cx="882650" cy="773430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7133,8 +7096,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15396845" y="3650615"/>
-          <a:ext cx="1036955" cy="1031875"/>
+          <a:off x="15396845" y="3564890"/>
+          <a:ext cx="1036955" cy="917575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11182,2339 +11145,2338 @@
   <dimension ref="A2:Y104"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.83333333333333" style="20"/>
-    <col min="2" max="16" width="14.8333333333333" style="20" customWidth="1"/>
-    <col min="17" max="16384" width="8.83333333333333" style="20"/>
+    <col min="1" max="1" width="8.83333333333333" style="18"/>
+    <col min="2" max="16" width="14.8333333333333" style="18" customWidth="1"/>
+    <col min="17" max="16384" width="8.83333333333333" style="18"/>
   </cols>
   <sheetData>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9">
-      <c r="A2" s="24" t="s">
+    <row r="2" ht="31.5" customHeight="1" spans="1:14">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-    </row>
-    <row r="3" spans="14:14">
-      <c r="N3" s="41"/>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" s="20" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="N3" s="23"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3">
-      <c r="B5" s="20" t="s">
+    <row r="5" spans="1:14">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="20" t="s">
+    <row r="7" spans="1:14">
+      <c r="B7" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="20" t="s">
+    <row r="8" spans="1:14">
+      <c r="B8" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="20" t="s">
+    <row r="9" spans="1:14">
+      <c r="B9" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="1:14">
+      <c r="B11" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="20" t="s">
+    <row r="12" spans="1:14">
+      <c r="B12" s="18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="20" t="s">
+    <row r="13" spans="1:14">
+      <c r="B13" s="18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="20" t="s">
+    <row r="14" spans="1:14">
+      <c r="B14" s="18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="20" t="s">
+    <row r="15" spans="1:14">
+      <c r="B15" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B17" s="25" t="s">
+    <row r="17" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>0</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>1</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="25">
         <v>2</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>3</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>4</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>5</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>6</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="25">
         <v>7</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="25">
         <v>8</v>
       </c>
-      <c r="L17" s="26">
+      <c r="L17" s="25">
         <v>9</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="25">
         <v>10</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="25">
         <v>10</v>
       </c>
-      <c r="O17" s="26">
+      <c r="O17" s="25">
         <v>10</v>
       </c>
     </row>
-    <row r="18" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B18" s="25" t="s">
+    <row r="18" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="28" t="s">
+      <c r="J18" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="L18" s="28" t="s">
+      <c r="L18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="27" t="s">
+      <c r="M18" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="27" t="s">
+      <c r="N18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="O18" s="27" t="s">
+      <c r="O18" s="26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B19" s="25" t="s">
+    <row r="19" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="J19" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="L19" s="29" t="s">
+      <c r="L19" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="27">
         <v>10</v>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="27">
         <v>9</v>
       </c>
-      <c r="O19" s="29" t="s">
+      <c r="O19" s="27" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B20" s="25" t="s">
+    <row r="20" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B20" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-    </row>
-    <row r="21" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B21" s="25"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-    </row>
-    <row r="22" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B22" s="25"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-    </row>
-    <row r="23" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B23" s="25"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-    </row>
-    <row r="24" s="23" customFormat="1" ht="17.25" spans="2:15">
-      <c r="B24" s="25"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+    </row>
+    <row r="21" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B21" s="24"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+    </row>
+    <row r="22" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B22" s="24"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+    </row>
+    <row r="23" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B23" s="24"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+    </row>
+    <row r="24" s="21" customFormat="1" ht="15" spans="2:23">
+      <c r="B24" s="24"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
     </row>
     <row r="25" ht="17" customHeight="1"/>
     <row r="26" ht="17" customHeight="1"/>
     <row r="27" ht="17" customHeight="1"/>
-    <row r="28" ht="17" customHeight="1" spans="2:7">
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
+    <row r="28" ht="17" customHeight="1" spans="2:23">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" ht="17" customHeight="1" spans="2:23">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="W29" s="42"/>
+      <c r="W29" s="32"/>
     </row>
     <row r="30" ht="17" customHeight="1" spans="2:23">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="W30" s="42"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="W30" s="32"/>
     </row>
     <row r="31" ht="17" customHeight="1" spans="2:23">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="34">
         <v>1000</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="33">
         <v>100</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="33">
         <v>50</v>
       </c>
-      <c r="W31" s="42"/>
+      <c r="W31" s="32"/>
     </row>
     <row r="32" ht="17" customHeight="1" spans="2:23">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="33">
         <v>800</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="33">
         <v>100</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <v>35</v>
       </c>
-      <c r="W32" s="42"/>
+      <c r="W32" s="32"/>
     </row>
     <row r="33" spans="2:23">
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="33">
         <v>800</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="33">
         <v>100</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="33">
         <v>30</v>
       </c>
-      <c r="W33" s="42"/>
+      <c r="W33" s="32"/>
     </row>
     <row r="34" spans="2:23">
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="34" t="s">
+      <c r="D34" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="33">
         <v>300</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="33">
         <v>50</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="33">
         <v>20</v>
       </c>
-      <c r="W34" s="42"/>
+      <c r="W34" s="32"/>
     </row>
     <row r="35" spans="2:23">
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="34" t="s">
+      <c r="D35" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="33">
         <v>300</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="33">
         <v>35</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="33">
         <v>15</v>
       </c>
-      <c r="W35" s="42"/>
+      <c r="W35" s="32"/>
     </row>
     <row r="36" spans="2:23">
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="34" t="s">
+      <c r="D36" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="33">
         <v>200</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="33">
         <v>30</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="33">
         <v>10</v>
       </c>
-      <c r="W36" s="42"/>
+      <c r="W36" s="32"/>
     </row>
     <row r="37" spans="2:23">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="34">
+      <c r="E37" s="33">
         <v>200</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="33">
         <v>20</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="33">
         <v>10</v>
       </c>
-      <c r="W37" s="42"/>
+      <c r="W37" s="32"/>
     </row>
     <row r="38" spans="2:23">
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="33">
         <v>100</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="33">
         <v>15</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="33">
         <v>10</v>
       </c>
-      <c r="W38" s="42"/>
+      <c r="W38" s="32"/>
     </row>
     <row r="39" spans="2:23">
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D39" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="33">
         <v>100</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="33">
         <v>15</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="33">
         <v>10</v>
       </c>
-      <c r="W39" s="42"/>
+      <c r="W39" s="32"/>
     </row>
     <row r="40" spans="2:23">
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="34">
+      <c r="E40" s="33">
         <v>100</v>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="33">
         <v>15</v>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="33">
         <v>5</v>
       </c>
-      <c r="W40" s="42"/>
+      <c r="W40" s="32"/>
     </row>
     <row r="41" spans="2:23">
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="C41" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="33">
         <v>100</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="33">
         <v>10</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="33">
         <v>5</v>
       </c>
-      <c r="W41" s="42"/>
+      <c r="W41" s="32"/>
     </row>
     <row r="42" spans="2:23">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="33">
         <v>50</v>
       </c>
-      <c r="F42" s="36">
+      <c r="F42" s="35">
         <v>10</v>
       </c>
-      <c r="G42" s="36">
+      <c r="G42" s="35">
         <v>5</v>
       </c>
-      <c r="W42" s="42"/>
-    </row>
-    <row r="43" spans="23:23">
-      <c r="W43" s="42"/>
+      <c r="W42" s="32"/>
+    </row>
+    <row r="43" spans="2:23">
+      <c r="W43" s="32"/>
     </row>
     <row r="44" spans="2:23">
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="I44" s="37" t="s">
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="I44" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="37"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
-      <c r="W44" s="42"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="W44" s="32"/>
     </row>
     <row r="45" spans="2:23">
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="33" t="s">
+      <c r="D45" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="33" t="s">
+      <c r="E45" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="G45" s="33" t="s">
+      <c r="G45" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="33" t="s">
+      <c r="I45" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="J45" s="33" t="s">
+      <c r="J45" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="K45" s="33" t="s">
+      <c r="K45" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="L45" s="33" t="s">
+      <c r="L45" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="M45" s="33" t="s">
+      <c r="M45" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="N45" s="33" t="s">
+      <c r="N45" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="W45" s="42"/>
+      <c r="W45" s="32"/>
     </row>
     <row r="46" spans="2:23">
-      <c r="B46" s="38">
+      <c r="B46" s="37">
         <v>0</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G46" s="39" t="s">
+      <c r="G46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="38">
+      <c r="I46" s="37">
         <v>0</v>
       </c>
-      <c r="J46" s="39" t="s">
+      <c r="J46" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="K46" s="39" t="s">
+      <c r="K46" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="L46" s="39" t="s">
+      <c r="L46" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="M46" s="39" t="s">
+      <c r="M46" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="N46" s="39" t="s">
+      <c r="N46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="W46" s="42"/>
+      <c r="W46" s="32"/>
     </row>
     <row r="47" spans="2:23">
-      <c r="B47" s="38">
+      <c r="B47" s="37">
         <v>1</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="39" t="s">
+      <c r="D47" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="39" t="s">
+      <c r="E47" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="38">
+      <c r="I47" s="37">
         <v>1</v>
       </c>
-      <c r="J47" s="39" t="s">
+      <c r="J47" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="39" t="s">
+      <c r="K47" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="L47" s="39" t="s">
+      <c r="L47" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M47" s="39" t="s">
+      <c r="M47" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="N47" s="39" t="s">
+      <c r="N47" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="W47" s="42"/>
+      <c r="W47" s="32"/>
     </row>
     <row r="48" spans="2:23">
-      <c r="B48" s="38">
+      <c r="B48" s="37">
         <v>2</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="39" t="s">
+      <c r="E48" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="G48" s="39" t="s">
+      <c r="G48" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="38">
+      <c r="I48" s="37">
         <v>2</v>
       </c>
-      <c r="J48" s="39" t="s">
+      <c r="J48" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="39" t="s">
+      <c r="K48" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="L48" s="39" t="s">
+      <c r="L48" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="M48" s="39" t="s">
+      <c r="M48" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="N48" s="39" t="s">
+      <c r="N48" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="W48" s="42"/>
+      <c r="W48" s="32"/>
     </row>
     <row r="49" spans="2:23">
-      <c r="B49" s="38">
+      <c r="B49" s="37">
         <v>3</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="40" t="s">
+      <c r="D49" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="39" t="s">
+      <c r="E49" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F49" s="39" t="s">
+      <c r="F49" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G49" s="39" t="s">
+      <c r="G49" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I49" s="38">
+      <c r="I49" s="37">
         <v>3</v>
       </c>
-      <c r="J49" s="39" t="s">
+      <c r="J49" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K49" s="40" t="s">
+      <c r="K49" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="39" t="s">
+      <c r="L49" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="M49" s="39" t="s">
+      <c r="M49" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="N49" s="39" t="s">
+      <c r="N49" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="W49" s="42"/>
+      <c r="W49" s="32"/>
     </row>
     <row r="50" spans="2:23">
-      <c r="B50" s="38">
+      <c r="B50" s="37">
         <v>4</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="D50" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E50" s="39" t="s">
+      <c r="E50" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="39" t="s">
+      <c r="G50" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I50" s="38">
+      <c r="I50" s="37">
         <v>4</v>
       </c>
-      <c r="J50" s="39" t="s">
+      <c r="J50" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="K50" s="40" t="s">
+      <c r="K50" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="L50" s="39" t="s">
+      <c r="L50" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M50" s="39" t="s">
+      <c r="M50" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="N50" s="39" t="s">
+      <c r="N50" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="W50" s="42"/>
+      <c r="W50" s="32"/>
     </row>
     <row r="51" spans="2:23">
-      <c r="B51" s="38">
+      <c r="B51" s="37">
         <v>5</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="40" t="s">
+      <c r="D51" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="39" t="s">
+      <c r="E51" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I51" s="38">
+      <c r="I51" s="37">
         <v>5</v>
       </c>
-      <c r="J51" s="39" t="s">
+      <c r="J51" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="K51" s="40" t="s">
+      <c r="K51" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="L51" s="39" t="s">
+      <c r="L51" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M51" s="39" t="s">
+      <c r="M51" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="N51" s="39" t="s">
+      <c r="N51" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="W51" s="42"/>
+      <c r="W51" s="32"/>
     </row>
     <row r="52" spans="2:23">
-      <c r="B52" s="38">
+      <c r="B52" s="37">
         <v>6</v>
       </c>
-      <c r="C52" s="39" t="s">
+      <c r="C52" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E52" s="39" t="s">
+      <c r="E52" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F52" s="39" t="s">
+      <c r="F52" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G52" s="39" t="s">
+      <c r="G52" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I52" s="38">
+      <c r="I52" s="37">
         <v>6</v>
       </c>
-      <c r="J52" s="39" t="s">
+      <c r="J52" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K52" s="40" t="s">
+      <c r="K52" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="L52" s="39" t="s">
+      <c r="L52" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="M52" s="39" t="s">
+      <c r="M52" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="N52" s="39" t="s">
+      <c r="N52" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="W52" s="42"/>
+      <c r="W52" s="32"/>
     </row>
     <row r="53" spans="2:23">
-      <c r="B53" s="38">
+      <c r="B53" s="37">
         <v>7</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="39" t="s">
+      <c r="D53" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="39" t="s">
+      <c r="E53" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="G53" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I53" s="38">
+      <c r="I53" s="37">
         <v>7</v>
       </c>
-      <c r="J53" s="39" t="s">
+      <c r="J53" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K53" s="39" t="s">
+      <c r="K53" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L53" s="39" t="s">
+      <c r="L53" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M53" s="39" t="s">
+      <c r="M53" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="N53" s="39" t="s">
+      <c r="N53" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="W53" s="42"/>
+      <c r="W53" s="32"/>
     </row>
     <row r="54" spans="2:23">
-      <c r="B54" s="38">
+      <c r="B54" s="37">
         <v>8</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D54" s="39" t="s">
+      <c r="D54" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="39" t="s">
+      <c r="E54" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="G54" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I54" s="38">
+      <c r="I54" s="37">
         <v>8</v>
       </c>
-      <c r="J54" s="39" t="s">
+      <c r="J54" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K54" s="39" t="s">
+      <c r="K54" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="L54" s="39" t="s">
+      <c r="L54" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M54" s="39" t="s">
+      <c r="M54" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="N54" s="39" t="s">
+      <c r="N54" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="W54" s="42"/>
+      <c r="W54" s="32"/>
     </row>
     <row r="55" spans="2:23">
-      <c r="B55" s="38">
+      <c r="B55" s="37">
         <v>9</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="39" t="s">
+      <c r="D55" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="39" t="s">
+      <c r="E55" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F55" s="39" t="s">
+      <c r="F55" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I55" s="38">
+      <c r="I55" s="37">
         <v>9</v>
       </c>
-      <c r="J55" s="39" t="s">
+      <c r="J55" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="K55" s="39" t="s">
+      <c r="K55" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="L55" s="39" t="s">
+      <c r="L55" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M55" s="39" t="s">
+      <c r="M55" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="N55" s="39" t="s">
+      <c r="N55" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="W55" s="42"/>
+      <c r="W55" s="32"/>
     </row>
     <row r="56" spans="2:23">
-      <c r="B56" s="38">
+      <c r="B56" s="37">
         <v>10</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="39" t="s">
+      <c r="E56" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I56" s="38">
+      <c r="I56" s="37">
         <v>10</v>
       </c>
-      <c r="J56" s="39" t="s">
+      <c r="J56" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="39" t="s">
+      <c r="K56" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="L56" s="39" t="s">
+      <c r="L56" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="M56" s="39" t="s">
+      <c r="M56" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="N56" s="39" t="s">
+      <c r="N56" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="W56" s="42"/>
+      <c r="W56" s="32"/>
     </row>
     <row r="57" spans="2:23">
-      <c r="B57" s="38">
+      <c r="B57" s="37">
         <v>11</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="39" t="s">
+      <c r="E57" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I57" s="38">
+      <c r="I57" s="37">
         <v>11</v>
       </c>
-      <c r="J57" s="39" t="s">
+      <c r="J57" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="K57" s="39" t="s">
+      <c r="K57" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L57" s="39" t="s">
+      <c r="L57" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="M57" s="39" t="s">
+      <c r="M57" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="N57" s="39" t="s">
+      <c r="N57" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="W57" s="42"/>
+      <c r="W57" s="32"/>
     </row>
     <row r="58" spans="2:23">
-      <c r="B58" s="38">
+      <c r="B58" s="37">
         <v>12</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G58" s="39" t="s">
+      <c r="G58" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="38">
+      <c r="I58" s="37">
         <v>12</v>
       </c>
-      <c r="J58" s="39" t="s">
+      <c r="J58" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K58" s="39" t="s">
+      <c r="K58" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L58" s="39" t="s">
+      <c r="L58" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M58" s="39" t="s">
+      <c r="M58" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="N58" s="39" t="s">
+      <c r="N58" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="W58" s="42"/>
+      <c r="W58" s="32"/>
     </row>
     <row r="59" spans="2:23">
-      <c r="B59" s="38">
+      <c r="B59" s="37">
         <v>13</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="39" t="s">
+      <c r="D59" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E59" s="39" t="s">
+      <c r="E59" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F59" s="39" t="s">
+      <c r="F59" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="G59" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I59" s="38">
+      <c r="I59" s="37">
         <v>13</v>
       </c>
-      <c r="J59" s="39" t="s">
+      <c r="J59" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="K59" s="39" t="s">
+      <c r="K59" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="L59" s="39" t="s">
+      <c r="L59" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="M59" s="39" t="s">
+      <c r="M59" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="N59" s="39" t="s">
+      <c r="N59" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="W59" s="42"/>
+      <c r="W59" s="32"/>
     </row>
     <row r="60" spans="2:23">
-      <c r="B60" s="38">
+      <c r="B60" s="37">
         <v>14</v>
       </c>
-      <c r="C60" s="39" t="s">
+      <c r="C60" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D60" s="39" t="s">
+      <c r="D60" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F60" s="40" t="s">
+      <c r="F60" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="39" t="s">
+      <c r="G60" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I60" s="38">
+      <c r="I60" s="37">
         <v>14</v>
       </c>
-      <c r="J60" s="39" t="s">
+      <c r="J60" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="K60" s="39" t="s">
+      <c r="K60" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="L60" s="39" t="s">
+      <c r="L60" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="M60" s="40" t="s">
+      <c r="M60" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="N60" s="39" t="s">
+      <c r="N60" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="W60" s="42"/>
+      <c r="W60" s="32"/>
     </row>
     <row r="61" spans="2:23">
-      <c r="B61" s="38">
+      <c r="B61" s="37">
         <v>15</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="39" t="s">
+      <c r="D61" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E61" s="39" t="s">
+      <c r="E61" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F61" s="40" t="s">
+      <c r="F61" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I61" s="38">
+      <c r="I61" s="37">
         <v>15</v>
       </c>
-      <c r="J61" s="39" t="s">
+      <c r="J61" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K61" s="39" t="s">
+      <c r="K61" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="39" t="s">
+      <c r="L61" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M61" s="40" t="s">
+      <c r="M61" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="N61" s="39" t="s">
+      <c r="N61" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="W61" s="42"/>
+      <c r="W61" s="32"/>
     </row>
     <row r="62" spans="2:23">
-      <c r="B62" s="38">
+      <c r="B62" s="37">
         <v>16</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D62" s="39" t="s">
+      <c r="D62" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="39" t="s">
+      <c r="E62" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F62" s="40" t="s">
+      <c r="F62" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="G62" s="39" t="s">
+      <c r="G62" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I62" s="38">
+      <c r="I62" s="37">
         <v>16</v>
       </c>
-      <c r="J62" s="39" t="s">
+      <c r="J62" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="K62" s="39" t="s">
+      <c r="K62" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="L62" s="39" t="s">
+      <c r="L62" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="M62" s="40" t="s">
+      <c r="M62" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="N62" s="39" t="s">
+      <c r="N62" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="W62" s="42"/>
+      <c r="W62" s="32"/>
     </row>
     <row r="63" spans="2:23">
-      <c r="B63" s="38">
+      <c r="B63" s="37">
         <v>17</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D63" s="39" t="s">
+      <c r="D63" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="39" t="s">
+      <c r="E63" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F63" s="40" t="s">
+      <c r="F63" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="39" t="s">
+      <c r="G63" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I63" s="38">
+      <c r="I63" s="37">
         <v>17</v>
       </c>
-      <c r="J63" s="39" t="s">
+      <c r="J63" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K63" s="39" t="s">
+      <c r="K63" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="L63" s="39" t="s">
+      <c r="L63" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M63" s="40" t="s">
+      <c r="M63" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="N63" s="39" t="s">
+      <c r="N63" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="W63" s="42"/>
+      <c r="W63" s="32"/>
     </row>
     <row r="64" spans="2:23">
-      <c r="B64" s="38">
+      <c r="B64" s="37">
         <v>18</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="39" t="s">
+      <c r="D64" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="39" t="s">
+      <c r="E64" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F64" s="40" t="s">
+      <c r="F64" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G64" s="39" t="s">
+      <c r="G64" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="I64" s="38">
+      <c r="I64" s="37">
         <v>18</v>
       </c>
-      <c r="J64" s="39" t="s">
+      <c r="J64" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K64" s="39" t="s">
+      <c r="K64" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="L64" s="39" t="s">
+      <c r="L64" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="M64" s="40" t="s">
+      <c r="M64" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="N64" s="39" t="s">
+      <c r="N64" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="W64" s="42"/>
+      <c r="W64" s="32"/>
     </row>
     <row r="65" spans="2:23">
-      <c r="B65" s="38">
+      <c r="B65" s="37">
         <v>19</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="39" t="s">
+      <c r="D65" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E65" s="39" t="s">
+      <c r="E65" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="39" t="s">
+      <c r="F65" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="G65" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I65" s="38">
+      <c r="I65" s="37">
         <v>19</v>
       </c>
-      <c r="J65" s="39" t="s">
+      <c r="J65" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="K65" s="39" t="s">
+      <c r="K65" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="L65" s="39" t="s">
+      <c r="L65" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="M65" s="39" t="s">
+      <c r="M65" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="N65" s="39" t="s">
+      <c r="N65" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="W65" s="42"/>
-    </row>
-    <row r="66" spans="2:14">
-      <c r="B66" s="38">
+      <c r="W65" s="32"/>
+    </row>
+    <row r="66" spans="2:23">
+      <c r="B66" s="37">
         <v>20</v>
       </c>
-      <c r="C66" s="39" t="s">
+      <c r="C66" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="39" t="s">
+      <c r="D66" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E66" s="39" t="s">
+      <c r="E66" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F66" s="39" t="s">
+      <c r="F66" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G66" s="39" t="s">
+      <c r="G66" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I66" s="38">
+      <c r="I66" s="37">
         <v>20</v>
       </c>
-      <c r="J66" s="39" t="s">
+      <c r="J66" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="K66" s="39" t="s">
+      <c r="K66" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="L66" s="39" t="s">
+      <c r="L66" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M66" s="39" t="s">
+      <c r="M66" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="N66" s="39" t="s">
+      <c r="N66" s="38" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="2:14">
-      <c r="B67" s="38">
+    <row r="67" spans="2:23">
+      <c r="B67" s="37">
         <v>21</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="39" t="s">
+      <c r="D67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E67" s="39" t="s">
+      <c r="E67" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F67" s="39" t="s">
+      <c r="F67" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="G67" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I67" s="38">
+      <c r="I67" s="37">
         <v>21</v>
       </c>
-      <c r="J67" s="39" t="s">
+      <c r="J67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="39" t="s">
+      <c r="K67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="L67" s="39" t="s">
+      <c r="L67" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="M67" s="39" t="s">
+      <c r="M67" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="N67" s="39" t="s">
+      <c r="N67" s="38" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" ht="19" customHeight="1" spans="2:14">
-      <c r="B68" s="38">
+    <row r="68" ht="19" customHeight="1" spans="2:23">
+      <c r="B68" s="37">
         <v>22</v>
       </c>
-      <c r="C68" s="39" t="s">
+      <c r="C68" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="39" t="s">
+      <c r="D68" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="39" t="s">
+      <c r="E68" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="39" t="s">
+      <c r="F68" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="G68" s="39" t="s">
+      <c r="G68" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I68" s="38">
+      <c r="I68" s="37">
         <v>22</v>
       </c>
-      <c r="J68" s="39" t="s">
+      <c r="J68" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K68" s="39" t="s">
+      <c r="K68" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="L68" s="39" t="s">
+      <c r="L68" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="M68" s="39" t="s">
+      <c r="M68" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="N68" s="39" t="s">
+      <c r="N68" s="38" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="2:14">
-      <c r="B69" s="38">
+    <row r="69" spans="2:23">
+      <c r="B69" s="37">
         <v>23</v>
       </c>
-      <c r="C69" s="39" t="s">
+      <c r="C69" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="39" t="s">
+      <c r="D69" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="39" t="s">
+      <c r="E69" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="39" t="s">
+      <c r="F69" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="39" t="s">
+      <c r="G69" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I69" s="38">
+      <c r="I69" s="37">
         <v>23</v>
       </c>
-      <c r="J69" s="39" t="s">
+      <c r="J69" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K69" s="39" t="s">
+      <c r="K69" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L69" s="39" t="s">
+      <c r="L69" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M69" s="39" t="s">
+      <c r="M69" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="N69" s="39" t="s">
+      <c r="N69" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="2:14">
-      <c r="B70" s="38">
+    <row r="70" spans="2:23">
+      <c r="B70" s="37">
         <v>24</v>
       </c>
-      <c r="C70" s="39" t="s">
+      <c r="C70" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="39" t="s">
+      <c r="D70" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E70" s="39" t="s">
+      <c r="E70" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F70" s="39" t="s">
+      <c r="F70" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G70" s="39" t="s">
+      <c r="G70" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="I70" s="38">
+      <c r="I70" s="37">
         <v>24</v>
       </c>
-      <c r="J70" s="39" t="s">
+      <c r="J70" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="K70" s="39" t="s">
+      <c r="K70" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="L70" s="39" t="s">
+      <c r="L70" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="M70" s="39" t="s">
+      <c r="M70" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="N70" s="39" t="s">
+      <c r="N70" s="38" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="2:14">
-      <c r="B71" s="38">
+    <row r="71" spans="2:23">
+      <c r="B71" s="37">
         <v>25</v>
       </c>
-      <c r="C71" s="39" t="s">
+      <c r="C71" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="39" t="s">
+      <c r="D71" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E71" s="39" t="s">
+      <c r="E71" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F71" s="39" t="s">
+      <c r="F71" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="39" t="s">
+      <c r="G71" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I71" s="38">
+      <c r="I71" s="37">
         <v>25</v>
       </c>
-      <c r="J71" s="39" t="s">
+      <c r="J71" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="K71" s="39" t="s">
+      <c r="K71" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="39" t="s">
+      <c r="L71" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="M71" s="39" t="s">
+      <c r="M71" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="N71" s="39" t="s">
+      <c r="N71" s="38" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="2:14">
-      <c r="B72" s="38">
+    <row r="72" spans="2:23">
+      <c r="B72" s="37">
         <v>26</v>
       </c>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39" t="s">
+      <c r="C72" s="38"/>
+      <c r="D72" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="39" t="s">
+      <c r="E72" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39" t="s">
+      <c r="F72" s="38"/>
+      <c r="G72" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I72" s="38">
+      <c r="I72" s="37">
         <v>26</v>
       </c>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39" t="s">
+      <c r="J72" s="38"/>
+      <c r="K72" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="39" t="s">
+      <c r="L72" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="M72" s="39"/>
-      <c r="N72" s="39" t="s">
+      <c r="M72" s="38"/>
+      <c r="N72" s="38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="2:14">
-      <c r="B73" s="38">
+    <row r="73" spans="2:23">
+      <c r="B73" s="37">
         <v>27</v>
       </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39" t="s">
+      <c r="C73" s="38"/>
+      <c r="D73" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E73" s="39" t="s">
+      <c r="E73" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39" t="s">
+      <c r="F73" s="38"/>
+      <c r="G73" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I73" s="38">
+      <c r="I73" s="37">
         <v>27</v>
       </c>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39" t="s">
+      <c r="J73" s="38"/>
+      <c r="K73" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L73" s="39" t="s">
+      <c r="L73" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M73" s="39"/>
-      <c r="N73" s="39" t="s">
+      <c r="M73" s="38"/>
+      <c r="N73" s="38" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="2:14">
-      <c r="B74" s="38">
+    <row r="74" spans="2:23">
+      <c r="B74" s="37">
         <v>28</v>
       </c>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39" t="s">
+      <c r="C74" s="38"/>
+      <c r="D74" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39" t="s">
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I74" s="38">
+      <c r="I74" s="37">
         <v>28</v>
       </c>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39" t="s">
+      <c r="J74" s="38"/>
+      <c r="K74" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="L74" s="39"/>
-      <c r="M74" s="39"/>
-      <c r="N74" s="39" t="s">
+      <c r="L74" s="38"/>
+      <c r="M74" s="38"/>
+      <c r="N74" s="38" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="2:14">
-      <c r="B75" s="38">
+    <row r="75" spans="2:23">
+      <c r="B75" s="37">
         <v>29</v>
       </c>
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39" t="s">
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I75" s="38">
+      <c r="I75" s="37">
         <v>29</v>
       </c>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="39"/>
-      <c r="N75" s="39" t="s">
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
+      <c r="L75" s="38"/>
+      <c r="M75" s="38"/>
+      <c r="N75" s="38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="2:14">
-      <c r="B76" s="38">
+    <row r="76" spans="2:23">
+      <c r="B76" s="37">
         <v>30</v>
       </c>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39" t="s">
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="I76" s="38">
+      <c r="I76" s="37">
         <v>30</v>
       </c>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="39"/>
-      <c r="M76" s="39"/>
-      <c r="N76" s="39" t="s">
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
+      <c r="L76" s="38"/>
+      <c r="M76" s="38"/>
+      <c r="N76" s="38" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="2:14">
-      <c r="B77" s="38">
+    <row r="77" spans="2:23">
+      <c r="B77" s="37">
         <v>31</v>
       </c>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39" t="s">
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I77" s="38">
+      <c r="I77" s="37">
         <v>31</v>
       </c>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="39"/>
-      <c r="N77" s="39" t="s">
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="38"/>
+      <c r="M77" s="38"/>
+      <c r="N77" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="2:14">
-      <c r="B78" s="38">
+    <row r="78" spans="2:23">
+      <c r="B78" s="37">
         <v>32</v>
       </c>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39" t="s">
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I78" s="38">
+      <c r="I78" s="37">
         <v>32</v>
       </c>
-      <c r="J78" s="39"/>
-      <c r="K78" s="39"/>
-      <c r="L78" s="39"/>
-      <c r="M78" s="39"/>
-      <c r="N78" s="39" t="s">
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
+      <c r="L78" s="38"/>
+      <c r="M78" s="38"/>
+      <c r="N78" s="38" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="2:14">
-      <c r="B79" s="38">
+    <row r="79" spans="2:23">
+      <c r="B79" s="37">
         <v>33</v>
       </c>
-      <c r="C79" s="39"/>
-      <c r="D79" s="39"/>
-      <c r="E79" s="39"/>
-      <c r="F79" s="39"/>
-      <c r="G79" s="39" t="s">
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I79" s="38">
+      <c r="I79" s="37">
         <v>33</v>
       </c>
-      <c r="J79" s="39"/>
-      <c r="K79" s="39"/>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-      <c r="N79" s="39" t="s">
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="2:14">
-      <c r="B80" s="38">
+    <row r="80" spans="2:23">
+      <c r="B80" s="37">
         <v>34</v>
       </c>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39" t="s">
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="I80" s="38">
+      <c r="I80" s="37">
         <v>34</v>
       </c>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="39" t="s">
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
+      <c r="L80" s="38"/>
+      <c r="M80" s="38"/>
+      <c r="N80" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="82" spans="2:25">
-      <c r="B82" s="20" t="s">
+      <c r="B82" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="P82" s="21"/>
-      <c r="S82" s="21"/>
-      <c r="T82" s="21"/>
-      <c r="U82" s="21"/>
-      <c r="X82" s="21"/>
-      <c r="Y82" s="21"/>
-    </row>
-    <row r="83" spans="16:25">
-      <c r="P83" s="21"/>
-      <c r="S83" s="21"/>
-      <c r="T83" s="21"/>
-      <c r="U83" s="21"/>
-      <c r="X83" s="21"/>
-      <c r="Y83" s="21"/>
-    </row>
-    <row r="84" spans="2:21">
-      <c r="B84" s="43" t="s">
+      <c r="P82" s="19"/>
+      <c r="S82" s="19"/>
+      <c r="T82" s="19"/>
+      <c r="U82" s="19"/>
+      <c r="X82" s="19"/>
+      <c r="Y82" s="19"/>
+    </row>
+    <row r="83" spans="2:25">
+      <c r="P83" s="19"/>
+      <c r="S83" s="19"/>
+      <c r="T83" s="19"/>
+      <c r="U83" s="19"/>
+      <c r="X83" s="19"/>
+      <c r="Y83" s="19"/>
+    </row>
+    <row r="84" spans="2:25">
+      <c r="B84" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C84" s="44">
+      <c r="C84" s="41">
         <v>25</v>
       </c>
-      <c r="D84" s="21"/>
-      <c r="E84" s="43" t="s">
+      <c r="D84" s="19"/>
+      <c r="E84" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F84" s="44">
+      <c r="F84" s="41">
         <v>20</v>
       </c>
-      <c r="H84" s="43" t="s">
+      <c r="H84" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="I84" s="44">
+      <c r="I84" s="41">
         <v>15</v>
       </c>
-      <c r="J84" s="21"/>
-      <c r="K84" s="43" t="s">
+      <c r="J84" s="19"/>
+      <c r="K84" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="L84" s="44">
+      <c r="L84" s="41">
         <v>10</v>
       </c>
-      <c r="N84" s="43" t="s">
+      <c r="N84" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="O84" s="44">
+      <c r="O84" s="41">
         <v>6</v>
       </c>
-      <c r="P84" s="21"/>
-      <c r="U84" s="21"/>
-    </row>
-    <row r="85" spans="2:21">
-      <c r="B85" s="43" t="s">
+      <c r="P84" s="19"/>
+      <c r="U84" s="19"/>
+    </row>
+    <row r="85" spans="2:25">
+      <c r="B85" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C85" s="43" t="s">
+      <c r="C85" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="E85" s="43" t="s">
+      <c r="E85" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="F85" s="43" t="s">
+      <c r="F85" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="H85" s="43" t="s">
+      <c r="H85" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="I85" s="43" t="s">
+      <c r="I85" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="K85" s="43" t="s">
+      <c r="K85" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="L85" s="43" t="s">
+      <c r="L85" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="N85" s="43" t="s">
+      <c r="N85" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="O85" s="43" t="s">
+      <c r="O85" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="P85" s="21"/>
-      <c r="U85" s="21"/>
-    </row>
-    <row r="86" spans="2:21">
-      <c r="B86" s="44">
+      <c r="P85" s="19"/>
+      <c r="U85" s="19"/>
+    </row>
+    <row r="86" spans="2:25">
+      <c r="B86" s="41">
         <v>2</v>
       </c>
-      <c r="C86" s="44">
+      <c r="C86" s="41">
         <v>11</v>
       </c>
-      <c r="E86" s="44">
+      <c r="E86" s="41">
         <v>3</v>
       </c>
-      <c r="F86" s="44">
+      <c r="F86" s="41">
         <v>12</v>
       </c>
-      <c r="H86" s="44">
+      <c r="H86" s="41">
         <v>5</v>
       </c>
-      <c r="I86" s="44">
+      <c r="I86" s="41">
         <v>15</v>
       </c>
-      <c r="K86" s="44">
+      <c r="K86" s="41">
         <v>10</v>
       </c>
-      <c r="L86" s="44">
+      <c r="L86" s="41">
         <v>22</v>
       </c>
-      <c r="N86" s="44">
+      <c r="N86" s="41">
         <v>15</v>
       </c>
-      <c r="O86" s="44">
+      <c r="O86" s="41">
         <v>18</v>
       </c>
-      <c r="P86" s="21"/>
-      <c r="U86" s="21"/>
-    </row>
-    <row r="87" spans="2:21">
-      <c r="B87" s="44">
+      <c r="P86" s="19"/>
+      <c r="U86" s="19"/>
+    </row>
+    <row r="87" spans="2:25">
+      <c r="B87" s="41">
         <v>3</v>
       </c>
-      <c r="C87" s="44">
+      <c r="C87" s="41">
         <v>14</v>
       </c>
-      <c r="E87" s="44">
+      <c r="E87" s="41">
         <v>5</v>
       </c>
-      <c r="F87" s="44">
+      <c r="F87" s="41">
         <v>14</v>
       </c>
-      <c r="H87" s="44">
+      <c r="H87" s="41">
         <v>8</v>
       </c>
-      <c r="I87" s="44">
+      <c r="I87" s="41">
         <v>13</v>
       </c>
-      <c r="K87" s="44">
+      <c r="K87" s="41">
         <v>15</v>
       </c>
-      <c r="L87" s="44">
+      <c r="L87" s="41">
         <v>12</v>
       </c>
-      <c r="N87" s="44">
+      <c r="N87" s="41">
         <v>30</v>
       </c>
-      <c r="O87" s="44">
+      <c r="O87" s="41">
         <v>10</v>
       </c>
-      <c r="P87" s="21"/>
-      <c r="U87" s="21"/>
-    </row>
-    <row r="88" spans="2:21">
-      <c r="B88" s="44">
+      <c r="P87" s="19"/>
+      <c r="U87" s="19"/>
+    </row>
+    <row r="88" spans="2:25">
+      <c r="B88" s="41">
         <v>5</v>
       </c>
-      <c r="C88" s="44">
+      <c r="C88" s="41">
         <v>15</v>
       </c>
-      <c r="E88" s="44">
+      <c r="E88" s="41">
         <v>8</v>
       </c>
-      <c r="F88" s="44">
+      <c r="F88" s="41">
         <v>6</v>
       </c>
-      <c r="H88" s="44">
+      <c r="H88" s="41">
         <v>10</v>
       </c>
-      <c r="I88" s="44">
+      <c r="I88" s="41">
         <v>6</v>
       </c>
-      <c r="K88" s="44">
+      <c r="K88" s="41">
         <v>30</v>
       </c>
-      <c r="L88" s="44">
+      <c r="L88" s="41">
         <v>1</v>
       </c>
-      <c r="N88" s="44">
+      <c r="N88" s="41">
         <v>40</v>
       </c>
-      <c r="O88" s="44">
+      <c r="O88" s="41">
         <v>1</v>
       </c>
-      <c r="P88" s="21"/>
-      <c r="U88" s="21"/>
-    </row>
-    <row r="89" spans="2:21">
-      <c r="B89" s="43" t="s">
+      <c r="P88" s="19"/>
+      <c r="U88" s="19"/>
+    </row>
+    <row r="89" spans="2:25">
+      <c r="B89" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="43" t="s">
+      <c r="C89" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="E89" s="43" t="s">
+      <c r="E89" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="F89" s="43" t="s">
+      <c r="F89" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="H89" s="43" t="s">
+      <c r="H89" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="I89" s="43" t="s">
+      <c r="I89" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="K89" s="43" t="s">
+      <c r="K89" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="L89" s="43" t="s">
+      <c r="L89" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="N89" s="43" t="s">
+      <c r="N89" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="O89" s="43" t="s">
+      <c r="O89" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="P89" s="21"/>
-      <c r="U89" s="21"/>
-    </row>
-    <row r="90" spans="2:21">
-      <c r="B90" s="44">
+      <c r="P89" s="19"/>
+      <c r="U89" s="19"/>
+    </row>
+    <row r="90" spans="2:25">
+      <c r="B90" s="41">
         <v>0</v>
       </c>
-      <c r="C90" s="44">
+      <c r="C90" s="41">
         <v>8</v>
       </c>
-      <c r="E90" s="44">
+      <c r="E90" s="41">
         <v>0</v>
       </c>
-      <c r="F90" s="44">
+      <c r="F90" s="41">
         <v>8</v>
       </c>
-      <c r="H90" s="44">
+      <c r="H90" s="41">
         <v>0</v>
       </c>
-      <c r="I90" s="44">
+      <c r="I90" s="41">
         <v>8</v>
       </c>
-      <c r="K90" s="44">
+      <c r="K90" s="41">
         <v>0</v>
       </c>
-      <c r="L90" s="44">
+      <c r="L90" s="41">
         <v>14</v>
       </c>
-      <c r="N90" s="44">
+      <c r="N90" s="41">
         <v>0</v>
       </c>
-      <c r="O90" s="44">
+      <c r="O90" s="41">
         <v>9</v>
       </c>
-      <c r="P90" s="21"/>
-      <c r="U90" s="21"/>
-    </row>
-    <row r="91" spans="2:21">
-      <c r="B91" s="44">
+      <c r="P90" s="19"/>
+      <c r="U90" s="19"/>
+    </row>
+    <row r="91" spans="2:25">
+      <c r="B91" s="41">
         <v>1</v>
       </c>
-      <c r="C91" s="44">
+      <c r="C91" s="41">
         <v>14</v>
       </c>
-      <c r="E91" s="44">
+      <c r="E91" s="41">
         <v>1</v>
       </c>
-      <c r="F91" s="44">
+      <c r="F91" s="41">
         <v>14</v>
       </c>
-      <c r="H91" s="44">
+      <c r="H91" s="41">
         <v>1</v>
       </c>
-      <c r="I91" s="44">
+      <c r="I91" s="41">
         <v>14</v>
       </c>
-      <c r="K91" s="44">
+      <c r="K91" s="41">
         <v>1</v>
       </c>
-      <c r="L91" s="44">
+      <c r="L91" s="41">
         <v>14</v>
       </c>
-      <c r="N91" s="44">
+      <c r="N91" s="41">
         <v>1</v>
       </c>
-      <c r="O91" s="44">
+      <c r="O91" s="41">
         <v>14</v>
       </c>
-      <c r="P91" s="21"/>
-      <c r="U91" s="21"/>
-    </row>
-    <row r="92" spans="2:21">
-      <c r="B92" s="44">
+      <c r="P91" s="19"/>
+      <c r="U91" s="19"/>
+    </row>
+    <row r="92" spans="2:25">
+      <c r="B92" s="41">
         <v>2</v>
       </c>
-      <c r="C92" s="44">
+      <c r="C92" s="41">
         <v>12</v>
       </c>
-      <c r="E92" s="44">
+      <c r="E92" s="41">
         <v>2</v>
       </c>
-      <c r="F92" s="44">
+      <c r="F92" s="41">
         <v>12</v>
       </c>
-      <c r="H92" s="44">
+      <c r="H92" s="41">
         <v>2</v>
       </c>
-      <c r="I92" s="44">
+      <c r="I92" s="41">
         <v>13</v>
       </c>
-      <c r="K92" s="44">
+      <c r="K92" s="41">
         <v>2</v>
       </c>
-      <c r="L92" s="44">
+      <c r="L92" s="41">
         <v>8</v>
       </c>
-      <c r="N92" s="44">
+      <c r="N92" s="41">
         <v>2</v>
       </c>
-      <c r="O92" s="44">
+      <c r="O92" s="41">
         <v>14</v>
       </c>
-      <c r="P92" s="21"/>
-      <c r="U92" s="21"/>
-    </row>
-    <row r="93" spans="2:15">
-      <c r="B93" s="44">
+      <c r="P92" s="19"/>
+      <c r="U92" s="19"/>
+    </row>
+    <row r="93" spans="2:25">
+      <c r="B93" s="41">
         <v>3</v>
       </c>
-      <c r="C93" s="44">
+      <c r="C93" s="41">
         <v>5</v>
       </c>
-      <c r="E93" s="44">
+      <c r="E93" s="41">
         <v>3</v>
       </c>
-      <c r="F93" s="44">
+      <c r="F93" s="41">
         <v>5</v>
       </c>
-      <c r="H93" s="44">
+      <c r="H93" s="41">
         <v>3</v>
       </c>
-      <c r="I93" s="44">
+      <c r="I93" s="41">
         <v>5</v>
       </c>
-      <c r="K93" s="44">
+      <c r="K93" s="41">
         <v>3</v>
       </c>
-      <c r="L93" s="44">
+      <c r="L93" s="41">
         <v>4</v>
       </c>
-      <c r="N93" s="44">
+      <c r="N93" s="41">
         <v>3</v>
       </c>
-      <c r="O93" s="44">
+      <c r="O93" s="41">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="20" t="s">
+    <row r="95" spans="2:25">
+      <c r="B95" s="18" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="43" t="s">
+      <c r="B97" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C97" s="43" t="s">
+      <c r="C97" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D97" s="20"/>
-      <c r="E97" s="43" t="s">
+      <c r="E97" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="F97" s="43" t="s">
+      <c r="F97" s="40" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="43">
+      <c r="B98" s="40">
         <v>25</v>
       </c>
-      <c r="C98" s="44">
+      <c r="C98" s="41">
         <v>1</v>
       </c>
-      <c r="E98" s="43" t="s">
+      <c r="E98" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="F98" s="44">
+      <c r="F98" s="41">
         <v>15</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="43">
+      <c r="B99" s="40">
         <v>20</v>
       </c>
-      <c r="C99" s="44">
+      <c r="C99" s="41">
         <v>3</v>
       </c>
-      <c r="E99" s="43" t="s">
+      <c r="E99" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="F99" s="44">
+      <c r="F99" s="41">
         <v>56</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="43">
+      <c r="B100" s="40">
         <v>15</v>
       </c>
-      <c r="C100" s="44">
+      <c r="C100" s="41">
         <v>5</v>
       </c>
-      <c r="E100" s="43" t="s">
+      <c r="E100" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F100" s="44">
+      <c r="F100" s="41">
         <v>60</v>
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="43">
+      <c r="B101" s="40">
         <v>10</v>
       </c>
-      <c r="C101" s="44">
+      <c r="C101" s="41">
         <v>4</v>
       </c>
-      <c r="E101" s="43" t="s">
+      <c r="E101" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="F101" s="44">
+      <c r="F101" s="41">
         <v>10</v>
       </c>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="43">
+      <c r="B102" s="40">
         <v>6</v>
       </c>
-      <c r="C102" s="44">
+      <c r="C102" s="41">
         <v>1</v>
       </c>
-      <c r="E102" s="43" t="s">
+      <c r="E102" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F102" s="44">
+      <c r="F102" s="41">
         <v>10</v>
       </c>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="21"/>
-      <c r="C103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-    </row>
-    <row r="104" spans="2:3">
-      <c r="B104" s="21"/>
-      <c r="C104" s="21"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="19"/>
+      <c r="C104" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -13548,29 +13510,29 @@
   <dimension ref="B2:N2"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="8.83333333333333" style="20"/>
-    <col min="2" max="4" width="15.6666666666667" style="21" customWidth="1"/>
-    <col min="5" max="6" width="8.83333333333333" style="20"/>
-    <col min="7" max="9" width="15.6666666666667" style="21" customWidth="1"/>
-    <col min="10" max="11" width="8.83333333333333" style="20"/>
-    <col min="12" max="14" width="15.6666666666667" style="21" customWidth="1"/>
-    <col min="15" max="16384" width="8.83333333333333" style="20"/>
+    <col min="1" max="1" width="8.83333333333333" style="18"/>
+    <col min="2" max="4" width="15.6666666666667" style="19" customWidth="1"/>
+    <col min="5" max="6" width="8.83333333333333" style="18"/>
+    <col min="7" max="9" width="15.6666666666667" style="19" customWidth="1"/>
+    <col min="10" max="11" width="8.83333333333333" style="18"/>
+    <col min="12" max="14" width="15.6666666666667" style="19" customWidth="1"/>
+    <col min="15" max="16384" width="8.83333333333333" style="18"/>
   </cols>
   <sheetData>
     <row r="2" ht="20.25" spans="2:14">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="G2" s="22" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="G2" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13586,51 +13548,51 @@
   <dimension ref="B2:R30"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="11" style="20"/>
+    <col min="1" max="16384" width="11" style="18"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:2">
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="18" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="11" spans="2:2">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="30" spans="18:18">
-      <c r="R30" s="45" t="s">
+      <c r="R30" s="42" t="s">
         <v>89</v>
       </c>
     </row>
@@ -13673,37 +13635,37 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:38">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="15"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="7"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
@@ -13727,25 +13689,25 @@
       <c r="AL1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:38">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="15"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="7"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
@@ -13769,37 +13731,37 @@
       <c r="AL2" s="3"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:38">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="15"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="7"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -13823,25 +13785,25 @@
       <c r="AL3" s="3"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:38">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="15"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="7"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -13865,37 +13827,37 @@
       <c r="AL4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:38">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="15"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="7"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -13918,34 +13880,28 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="10:16">
-      <c r="J6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
+    <row r="6" spans="1:38">
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+    </row>
+    <row r="7" spans="1:38">
       <c r="A7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="2:16">
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:38">
       <c r="B8" s="3">
         <v>1000</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -13954,20 +13910,17 @@
       <c r="G8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="13" customHeight="1" spans="2:16">
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="13" customHeight="1" spans="1:38">
       <c r="B9" s="3">
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -13976,20 +13929,17 @@
       <c r="G9" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="2:16">
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:38">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>117</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -13998,20 +13948,17 @@
       <c r="G10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="2:16">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:38">
       <c r="B11" s="3">
         <v>1003</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>121</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -14020,20 +13967,17 @@
       <c r="G11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="2:16">
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:38">
       <c r="B12" s="3">
         <v>1004</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>125</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -14042,20 +13986,17 @@
       <c r="G12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="2:16">
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="1:38">
       <c r="B13" s="3">
         <v>1005</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -14064,20 +14005,17 @@
       <c r="G13" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="2:16">
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:38">
       <c r="B14" s="3">
         <v>1006</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>133</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -14086,20 +14024,17 @@
       <c r="G14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="2:16">
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:38">
       <c r="B15" s="3">
         <v>1007</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>137</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -14108,23 +14043,20 @@
       <c r="G15" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:6">
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:38">
       <c r="A16" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B16" s="3">
         <v>1008</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="2:16">
       <c r="B17" s="3">
@@ -14145,11 +14077,8 @@
       <c r="G17" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="2:16">
       <c r="B18" s="3">
@@ -14170,11 +14099,8 @@
       <c r="G18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="2:16">
       <c r="B19" s="3">
@@ -14195,11 +14121,8 @@
       <c r="G19" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="2:16">
       <c r="B20" s="3">
@@ -14220,11 +14143,8 @@
       <c r="G20" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="2:16">
       <c r="B21" s="3">
@@ -14245,11 +14165,8 @@
       <c r="G21" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="2:16">
       <c r="B22" s="3">
@@ -14264,17 +14181,14 @@
       <c r="E22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="2:16">
       <c r="B23" s="3">
@@ -14295,11 +14209,8 @@
       <c r="G23" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="2:16">
       <c r="B24" s="3">
@@ -14320,13 +14231,10 @@
       <c r="G24" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="2:7">
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="2:16">
       <c r="B25" s="3">
         <v>1017</v>
       </c>
@@ -14346,7 +14254,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" spans="2:7">
+    <row r="26" s="3" customFormat="1" spans="2:16">
       <c r="B26" s="3">
         <v>1018</v>
       </c>
@@ -14366,7 +14274,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" spans="2:7">
+    <row r="27" s="3" customFormat="1" spans="2:16">
       <c r="B27" s="3">
         <v>1019</v>
       </c>
@@ -14386,7 +14294,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="2:7">
+    <row r="28" s="3" customFormat="1" spans="2:16">
       <c r="B28" s="3">
         <v>1020</v>
       </c>
@@ -14406,22 +14314,22 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" spans="2:5">
+    <row r="29" s="3" customFormat="1" spans="2:16">
       <c r="B29" s="3">
         <v>1021</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="30" s="3" customFormat="1" spans="2:7">
+    <row r="30" s="3" customFormat="1" spans="2:16">
       <c r="B30" s="3">
         <v>1022</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -14431,14 +14339,14 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" spans="2:7">
+    <row r="31" s="3" customFormat="1" spans="2:16">
       <c r="B31" s="3">
         <v>1023</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>206</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -14448,14 +14356,14 @@
         <v>207</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" spans="2:7">
+    <row r="32" s="3" customFormat="1" spans="2:16">
       <c r="B32" s="3">
         <v>1024</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>209</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -14472,7 +14380,7 @@
       <c r="C33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>213</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -14489,7 +14397,7 @@
       <c r="C34" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>216</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -14506,7 +14414,7 @@
       <c r="C35" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>219</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -14523,7 +14431,7 @@
       <c r="C36" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>223</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -14540,7 +14448,7 @@
       <c r="C37" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>226</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -14557,7 +14465,7 @@
       <c r="C38" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>229</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -14567,11 +14475,11 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" s="3" customFormat="1" spans="2:5">
+    <row r="39" s="3" customFormat="1" spans="2:7">
       <c r="B39" s="3">
         <v>1031</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="14" t="s">
         <v>232</v>
       </c>
     </row>
@@ -14582,7 +14490,7 @@
       <c r="C40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>234</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -14599,7 +14507,7 @@
       <c r="C41" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>236</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -15000,7 +14908,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="65" s="3" customFormat="1" spans="2:7">
+    <row r="65" s="3" customFormat="1" spans="1:7">
       <c r="B65" s="3">
         <v>1057</v>
       </c>
@@ -15017,7 +14925,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="66" s="3" customFormat="1" spans="2:7">
+    <row r="66" s="3" customFormat="1" spans="1:7">
       <c r="B66" s="3">
         <v>1058</v>
       </c>
@@ -15034,7 +14942,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="67" s="3" customFormat="1" spans="2:7">
+    <row r="67" s="3" customFormat="1" spans="1:7">
       <c r="B67" s="3">
         <v>1059</v>
       </c>
@@ -15051,7 +14959,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="68" s="3" customFormat="1" spans="2:7">
+    <row r="68" s="3" customFormat="1" spans="1:7">
       <c r="B68" s="3">
         <v>1060</v>
       </c>
@@ -15068,7 +14976,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="69" s="3" customFormat="1" spans="2:7">
+    <row r="69" s="3" customFormat="1" spans="1:7">
       <c r="B69" s="3">
         <v>1061</v>
       </c>
@@ -15085,7 +14993,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="70" s="3" customFormat="1" spans="2:7">
+    <row r="70" s="3" customFormat="1" spans="1:7">
       <c r="B70" s="3">
         <v>1062</v>
       </c>
@@ -15105,7 +15013,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" s="3" customFormat="1" spans="2:7">
+    <row r="71" s="3" customFormat="1" spans="1:7">
       <c r="B71" s="3">
         <v>1063</v>
       </c>
@@ -15122,25 +15030,25 @@
         <v>358</v>
       </c>
     </row>
-    <row r="72" s="3" customFormat="1" spans="1:5">
+    <row r="72" s="3" customFormat="1" spans="1:7">
       <c r="A72" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B72" s="3">
         <v>1064</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="14" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="73" s="3" customFormat="1" spans="2:7">
+    <row r="73" s="3" customFormat="1" spans="1:7">
       <c r="B73" s="3">
         <v>1065</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="3" t="s">
         <v>361</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -15150,14 +15058,14 @@
         <v>363</v>
       </c>
     </row>
-    <row r="74" s="3" customFormat="1" spans="2:7">
+    <row r="74" s="3" customFormat="1" spans="1:7">
       <c r="B74" s="3">
         <v>1066</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="3" t="s">
         <v>365</v>
       </c>
       <c r="F74" s="3" t="s">
@@ -15167,7 +15075,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="75" spans="2:7">
+    <row r="75" spans="1:7">
       <c r="B75" s="3">
         <v>1067</v>
       </c>
@@ -15184,7 +15092,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="76" spans="2:7">
+    <row r="76" spans="1:7">
       <c r="B76" s="3">
         <v>1068</v>
       </c>
@@ -15201,7 +15109,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="77" spans="2:7">
+    <row r="77" spans="1:7">
       <c r="B77" s="3">
         <v>1069</v>
       </c>
@@ -15218,7 +15126,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="78" spans="2:7">
+    <row r="78" spans="1:7">
       <c r="B78" s="3">
         <v>1070</v>
       </c>
@@ -15235,19 +15143,19 @@
         <v>380</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:7">
       <c r="A79" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B79" s="3">
         <v>1071</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="F79" s="7"/>
-    </row>
-    <row r="80" spans="2:7">
+      <c r="F79" s="14"/>
+    </row>
+    <row r="80" spans="1:7">
       <c r="B80" s="3">
         <v>1072</v>
       </c>
@@ -15260,14 +15168,14 @@
       <c r="E80" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="3" t="s">
         <v>385</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="1:7">
       <c r="B81" s="3">
         <v>1073</v>
       </c>
@@ -15280,14 +15188,14 @@
       <c r="E81" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="3" t="s">
         <v>390</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="1:7">
       <c r="B82" s="3">
         <v>1074</v>
       </c>
@@ -15297,14 +15205,14 @@
       <c r="E82" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="3" t="s">
         <v>394</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="1:7">
       <c r="B83" s="3">
         <v>1075</v>
       </c>
@@ -15317,14 +15225,14 @@
       <c r="E83" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="3" t="s">
         <v>399</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="1:7">
       <c r="B84" s="3">
         <v>1076</v>
       </c>
@@ -15334,14 +15242,14 @@
       <c r="E84" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="3" t="s">
         <v>402</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="1:7">
       <c r="B85" s="3">
         <v>1077</v>
       </c>
@@ -15354,14 +15262,14 @@
       <c r="E85" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="3" t="s">
         <v>406</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="1:7">
       <c r="B86" s="3">
         <v>1078</v>
       </c>
@@ -15378,7 +15286,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="1:7">
       <c r="B87" s="3">
         <v>1079</v>
       </c>
@@ -15398,7 +15306,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="1:7">
       <c r="B88" s="3">
         <v>1080</v>
       </c>
@@ -15438,7 +15346,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="90" s="3" customFormat="1" spans="2:7">
+    <row r="90" s="3" customFormat="1" spans="1:7">
       <c r="B90" s="3">
         <v>1082</v>
       </c>
@@ -15455,7 +15363,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="1:7">
       <c r="B91" s="3">
         <v>1083</v>
       </c>
@@ -15475,7 +15383,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="1:7">
       <c r="B92" s="3">
         <v>1084</v>
       </c>
@@ -15495,7 +15403,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="93" spans="2:7">
+    <row r="93" spans="1:7">
       <c r="B93" s="3">
         <v>1085</v>
       </c>
@@ -15512,7 +15420,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="1:7">
       <c r="B94" s="3">
         <v>1086</v>
       </c>
@@ -15532,7 +15440,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="95" spans="2:7">
+    <row r="95" spans="1:7">
       <c r="B95" s="3">
         <v>1087</v>
       </c>
@@ -15552,7 +15460,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="96" spans="2:7">
+    <row r="96" spans="1:7">
       <c r="B96" s="3">
         <v>1088</v>
       </c>
@@ -16415,7 +16323,7 @@
       <c r="E143" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="F143" s="16" t="s">
+      <c r="F143" s="15" t="s">
         <v>646</v>
       </c>
       <c r="G143" s="3" t="s">
@@ -16435,7 +16343,7 @@
       <c r="E144" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="F144" s="16" t="s">
+      <c r="F144" s="15" t="s">
         <v>651</v>
       </c>
       <c r="G144" s="3" t="s">
@@ -16455,7 +16363,7 @@
       <c r="E145" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="F145" s="16" t="s">
+      <c r="F145" s="15" t="s">
         <v>656</v>
       </c>
       <c r="G145" s="3" t="s">
@@ -16472,7 +16380,7 @@
       <c r="E146" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="F146" s="16" t="s">
+      <c r="F146" s="15" t="s">
         <v>660</v>
       </c>
       <c r="G146" s="3" t="s">
@@ -16489,7 +16397,7 @@
       <c r="E147" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="F147" s="16" t="s">
+      <c r="F147" s="15" t="s">
         <v>664</v>
       </c>
       <c r="G147" s="3" t="s">
@@ -16506,7 +16414,7 @@
       <c r="E148" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="F148" s="16" t="s">
+      <c r="F148" s="15" t="s">
         <v>668</v>
       </c>
       <c r="G148" s="3" t="s">
@@ -16523,7 +16431,7 @@
       <c r="E149" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="F149" s="16" t="s">
+      <c r="F149" s="15" t="s">
         <v>672</v>
       </c>
       <c r="G149" s="3" t="s">
@@ -16540,7 +16448,7 @@
       <c r="E150" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F150" s="16" t="s">
+      <c r="F150" s="15" t="s">
         <v>676</v>
       </c>
       <c r="G150" s="3" t="s">
@@ -16557,7 +16465,7 @@
       <c r="E151" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="F151" s="16" t="s">
+      <c r="F151" s="15" t="s">
         <v>680</v>
       </c>
       <c r="G151" s="3" t="s">
@@ -16574,7 +16482,7 @@
       <c r="E152" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="F152" s="16" t="s">
+      <c r="F152" s="15" t="s">
         <v>684</v>
       </c>
       <c r="G152" s="3" t="s">
@@ -16591,7 +16499,7 @@
       <c r="E153" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="F153" s="16" t="s">
+      <c r="F153" s="15" t="s">
         <v>688</v>
       </c>
       <c r="G153" s="3" t="s">
@@ -16611,7 +16519,7 @@
       <c r="E154" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="F154" s="16" t="s">
+      <c r="F154" s="15" t="s">
         <v>692</v>
       </c>
       <c r="G154" s="3" t="s">
@@ -16631,7 +16539,7 @@
       <c r="E155" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="F155" s="16" t="s">
+      <c r="F155" s="15" t="s">
         <v>696</v>
       </c>
       <c r="G155" s="3" t="s">
@@ -16648,7 +16556,7 @@
       <c r="E156" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F156" s="16" t="s">
+      <c r="F156" s="15" t="s">
         <v>699</v>
       </c>
       <c r="G156" s="3" t="s">
@@ -16668,7 +16576,7 @@
       <c r="E157" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="F157" s="16" t="s">
+      <c r="F157" s="15" t="s">
         <v>704</v>
       </c>
       <c r="G157" s="3" t="s">
@@ -16688,7 +16596,7 @@
       <c r="E158" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="F158" s="16" t="s">
+      <c r="F158" s="15" t="s">
         <v>709</v>
       </c>
       <c r="G158" s="3" t="s">
@@ -16708,7 +16616,7 @@
       <c r="E159" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F159" s="16" t="s">
+      <c r="F159" s="15" t="s">
         <v>714</v>
       </c>
       <c r="G159" s="3" t="s">
@@ -16728,7 +16636,7 @@
       <c r="E160" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="F160" s="16" t="s">
+      <c r="F160" s="15" t="s">
         <v>719</v>
       </c>
       <c r="G160" s="3" t="s">
@@ -16745,7 +16653,7 @@
       <c r="E161" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="F161" s="16" t="s">
+      <c r="F161" s="15" t="s">
         <v>723</v>
       </c>
       <c r="G161" s="3" t="s">
@@ -16762,7 +16670,7 @@
       <c r="E162" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="F162" s="16" t="s">
+      <c r="F162" s="15" t="s">
         <v>727</v>
       </c>
       <c r="G162" s="3" t="s">
@@ -16779,7 +16687,7 @@
       <c r="E163" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="F163" s="16" t="s">
+      <c r="F163" s="15" t="s">
         <v>731</v>
       </c>
       <c r="G163" s="3" t="s">
@@ -16796,7 +16704,7 @@
       <c r="E164" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="F164" s="16" t="s">
+      <c r="F164" s="15" t="s">
         <v>735</v>
       </c>
       <c r="G164" s="3" t="s">
@@ -16813,7 +16721,7 @@
       <c r="E165" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="F165" s="16" t="s">
+      <c r="F165" s="15" t="s">
         <v>739</v>
       </c>
       <c r="G165" s="3" t="s">
@@ -16830,7 +16738,7 @@
       <c r="E166" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="F166" s="16" t="s">
+      <c r="F166" s="15" t="s">
         <v>743</v>
       </c>
       <c r="G166" s="3" t="s">
@@ -16847,7 +16755,7 @@
       <c r="E167" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="F167" s="16" t="s">
+      <c r="F167" s="15" t="s">
         <v>747</v>
       </c>
       <c r="G167" s="3" t="s">
@@ -16864,7 +16772,7 @@
       <c r="E168" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="F168" s="16" t="s">
+      <c r="F168" s="15" t="s">
         <v>751</v>
       </c>
       <c r="G168" s="3" t="s">
@@ -16881,7 +16789,7 @@
       <c r="E169" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="F169" s="16" t="s">
+      <c r="F169" s="15" t="s">
         <v>755</v>
       </c>
       <c r="G169" s="3" t="s">
@@ -16898,7 +16806,7 @@
       <c r="E170" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="F170" s="16" t="s">
+      <c r="F170" s="15" t="s">
         <v>759</v>
       </c>
       <c r="G170" s="3" t="s">
@@ -16915,7 +16823,7 @@
       <c r="E171" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="F171" s="16" t="s">
+      <c r="F171" s="15" t="s">
         <v>763</v>
       </c>
       <c r="G171" s="3" t="s">
@@ -16932,7 +16840,7 @@
       <c r="E172" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="F172" s="16" t="s">
+      <c r="F172" s="15" t="s">
         <v>767</v>
       </c>
       <c r="G172" s="3" t="s">
@@ -16949,7 +16857,7 @@
       <c r="E173" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="F173" s="16" t="s">
+      <c r="F173" s="15" t="s">
         <v>771</v>
       </c>
       <c r="G173" s="3" t="s">
@@ -16966,7 +16874,7 @@
       <c r="E174" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="F174" s="16" t="s">
+      <c r="F174" s="15" t="s">
         <v>775</v>
       </c>
       <c r="G174" s="3" t="s">
@@ -16983,7 +16891,7 @@
       <c r="E175" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="F175" s="16" t="s">
+      <c r="F175" s="15" t="s">
         <v>779</v>
       </c>
       <c r="G175" s="3" t="s">
@@ -17000,14 +16908,14 @@
       <c r="E176" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="F176" s="16" t="s">
+      <c r="F176" s="15" t="s">
         <v>783</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="177" spans="2:7">
+    <row r="177" spans="1:7">
       <c r="B177" s="3">
         <v>1169</v>
       </c>
@@ -17017,14 +16925,14 @@
       <c r="E177" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="F177" s="16" t="s">
+      <c r="F177" s="15" t="s">
         <v>787</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="178" spans="2:7">
+    <row r="178" spans="1:7">
       <c r="B178" s="3">
         <v>1170</v>
       </c>
@@ -17034,32 +16942,32 @@
       <c r="E178" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F178" s="16" t="s">
+      <c r="F178" s="15" t="s">
         <v>791</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:7">
       <c r="A179" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B179" s="3">
         <v>1171</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="14" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="180" spans="2:7">
+    <row r="180" spans="1:7">
       <c r="B180" s="3">
         <v>1172</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E180" s="3" t="s">
         <v>795</v>
       </c>
       <c r="F180" s="3" t="s">
@@ -17069,7 +16977,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="181" spans="2:7">
+    <row r="181" spans="1:7">
       <c r="B181" s="3">
         <v>1173</v>
       </c>
@@ -17079,7 +16987,7 @@
       <c r="D181" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E181" s="3" t="s">
         <v>799</v>
       </c>
       <c r="F181" s="3" t="s">
@@ -17089,14 +16997,14 @@
         <v>800</v>
       </c>
     </row>
-    <row r="182" spans="2:7">
+    <row r="182" spans="1:7">
       <c r="B182" s="3">
         <v>1174</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="E182" s="4" t="s">
+      <c r="E182" s="3" t="s">
         <v>802</v>
       </c>
       <c r="F182" s="3" t="s">
@@ -17106,14 +17014,14 @@
         <v>803</v>
       </c>
     </row>
-    <row r="183" spans="2:7">
+    <row r="183" spans="1:7">
       <c r="B183" s="3">
         <v>1175</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="E183" s="4" t="s">
+      <c r="E183" s="3" t="s">
         <v>805</v>
       </c>
       <c r="F183" s="3" t="s">
@@ -17123,14 +17031,14 @@
         <v>807</v>
       </c>
     </row>
-    <row r="184" spans="2:7">
+    <row r="184" spans="1:7">
       <c r="B184" s="3">
         <v>1176</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="E184" s="4" t="s">
+      <c r="E184" s="3" t="s">
         <v>809</v>
       </c>
       <c r="F184" s="3" t="s">
@@ -17140,25 +17048,25 @@
         <v>811</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:7">
       <c r="A185" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B185" s="3">
         <v>1177</v>
       </c>
-      <c r="E185" s="7" t="s">
+      <c r="E185" s="14" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="186" spans="2:7">
+    <row r="186" spans="1:7">
       <c r="B186" s="3">
         <v>1178</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E186" s="3" t="s">
         <v>814</v>
       </c>
       <c r="F186" s="3" t="s">
@@ -17168,7 +17076,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="187" spans="2:7">
+    <row r="187" spans="1:7">
       <c r="B187" s="3">
         <v>1179</v>
       </c>
@@ -17178,7 +17086,7 @@
       <c r="D187" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="E187" s="4" t="s">
+      <c r="E187" s="3" t="s">
         <v>819</v>
       </c>
       <c r="F187" s="3" t="s">
@@ -17188,14 +17096,14 @@
         <v>821</v>
       </c>
     </row>
-    <row r="188" spans="2:7">
+    <row r="188" spans="1:7">
       <c r="B188" s="3">
         <v>1180</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="E188" s="4" t="s">
+      <c r="E188" s="3" t="s">
         <v>823</v>
       </c>
       <c r="F188" s="3" t="s">
@@ -17205,14 +17113,14 @@
         <v>825</v>
       </c>
     </row>
-    <row r="189" spans="2:7">
+    <row r="189" spans="1:7">
       <c r="B189" s="3">
         <v>1181</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="E189" s="4" t="s">
+      <c r="E189" s="3" t="s">
         <v>827</v>
       </c>
       <c r="F189" s="3" t="s">
@@ -17222,7 +17130,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="190" spans="2:7">
+    <row r="190" spans="1:7">
       <c r="B190" s="3">
         <v>1182</v>
       </c>
@@ -17232,7 +17140,7 @@
       <c r="D190" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="E190" s="4" t="s">
+      <c r="E190" s="3" t="s">
         <v>831</v>
       </c>
       <c r="F190" s="3" t="s">
@@ -17242,14 +17150,14 @@
         <v>828</v>
       </c>
     </row>
-    <row r="191" spans="2:7">
+    <row r="191" spans="1:7">
       <c r="B191" s="3">
         <v>1183</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="E191" s="17" t="s">
+      <c r="E191" s="16" t="s">
         <v>833</v>
       </c>
       <c r="F191" s="3" t="s">
@@ -17259,14 +17167,14 @@
         <v>835</v>
       </c>
     </row>
-    <row r="192" spans="2:7">
+    <row r="192" spans="1:7">
       <c r="B192" s="3">
         <v>1184</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="E192" s="17" t="s">
+      <c r="E192" s="16" t="s">
         <v>837</v>
       </c>
       <c r="F192" s="3" t="s">
@@ -17283,7 +17191,7 @@
       <c r="C193" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="E193" s="17" t="s">
+      <c r="E193" s="16" t="s">
         <v>841</v>
       </c>
       <c r="F193" s="3" t="s">
@@ -17300,7 +17208,7 @@
       <c r="C194" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="E194" s="17" t="s">
+      <c r="E194" s="16" t="s">
         <v>845</v>
       </c>
       <c r="F194" s="3" t="s">
@@ -17317,7 +17225,7 @@
       <c r="C195" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="E195" s="17" t="s">
+      <c r="E195" s="16" t="s">
         <v>849</v>
       </c>
       <c r="F195" s="3" t="s">
@@ -17334,7 +17242,7 @@
       <c r="C196" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="E196" s="17" t="s">
+      <c r="E196" s="16" t="s">
         <v>853</v>
       </c>
       <c r="F196" s="3" t="s">
@@ -17351,7 +17259,7 @@
       <c r="C197" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="E197" s="17" t="s">
+      <c r="E197" s="16" t="s">
         <v>857</v>
       </c>
       <c r="F197" s="3" t="s">
@@ -17368,7 +17276,7 @@
       <c r="C198" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="E198" s="17" t="s">
+      <c r="E198" s="16" t="s">
         <v>861</v>
       </c>
       <c r="F198" s="3" t="s">
@@ -17385,7 +17293,7 @@
       <c r="C199" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="E199" s="17" t="s">
+      <c r="E199" s="16" t="s">
         <v>865</v>
       </c>
       <c r="F199" s="3" t="s">
@@ -17402,7 +17310,7 @@
       <c r="C200" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="E200" s="17" t="s">
+      <c r="E200" s="16" t="s">
         <v>869</v>
       </c>
       <c r="F200" s="3" t="s">
@@ -17419,7 +17327,7 @@
       <c r="C201" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="E201" s="17" t="s">
+      <c r="E201" s="16" t="s">
         <v>869</v>
       </c>
       <c r="F201" s="3" t="s">
@@ -17436,7 +17344,7 @@
       <c r="C202" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="E202" s="17" t="s">
+      <c r="E202" s="16" t="s">
         <v>869</v>
       </c>
       <c r="F202" s="3" t="s">
@@ -17453,7 +17361,7 @@
       <c r="C203" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="E203" s="17" t="s">
+      <c r="E203" s="16" t="s">
         <v>841</v>
       </c>
       <c r="F203" s="3" t="s">
@@ -17470,7 +17378,7 @@
       <c r="C204" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="E204" s="17" t="s">
+      <c r="E204" s="16" t="s">
         <v>845</v>
       </c>
       <c r="F204" s="3" t="s">
@@ -17487,7 +17395,7 @@
       <c r="C205" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="E205" s="17" t="s">
+      <c r="E205" s="16" t="s">
         <v>885</v>
       </c>
       <c r="F205" s="3" t="s">
@@ -17504,7 +17412,7 @@
       <c r="C206" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="E206" s="17" t="s">
+      <c r="E206" s="16" t="s">
         <v>889</v>
       </c>
       <c r="F206" s="3" t="s">
@@ -17521,7 +17429,7 @@
       <c r="C207" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="E207" s="17" t="s">
+      <c r="E207" s="16" t="s">
         <v>849</v>
       </c>
       <c r="F207" s="3" t="s">
@@ -17538,7 +17446,7 @@
       <c r="C208" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="E208" s="17" t="s">
+      <c r="E208" s="16" t="s">
         <v>853</v>
       </c>
       <c r="F208" s="3" t="s">
@@ -17548,14 +17456,14 @@
         <v>897</v>
       </c>
     </row>
-    <row r="209" s="3" customFormat="1" spans="2:7">
+    <row r="209" s="3" customFormat="1" spans="1:7">
       <c r="B209" s="3">
         <v>1201</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="E209" s="17" t="s">
+      <c r="E209" s="16" t="s">
         <v>833</v>
       </c>
       <c r="F209" s="3" t="s">
@@ -17565,14 +17473,14 @@
         <v>900</v>
       </c>
     </row>
-    <row r="210" s="3" customFormat="1" spans="2:7">
+    <row r="210" s="3" customFormat="1" spans="1:7">
       <c r="B210" s="3">
         <v>1202</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="E210" s="17" t="s">
+      <c r="E210" s="16" t="s">
         <v>837</v>
       </c>
       <c r="F210" s="3" t="s">
@@ -17582,14 +17490,14 @@
         <v>903</v>
       </c>
     </row>
-    <row r="211" s="3" customFormat="1" spans="2:7">
+    <row r="211" s="3" customFormat="1" spans="1:7">
       <c r="B211" s="3">
         <v>1203</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="E211" s="17" t="s">
+      <c r="E211" s="16" t="s">
         <v>905</v>
       </c>
       <c r="F211" s="3" t="s">
@@ -17599,14 +17507,14 @@
         <v>907</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="1" spans="2:7">
+    <row r="212" s="3" customFormat="1" spans="1:7">
       <c r="B212" s="3">
         <v>1204</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="E212" s="17" t="s">
+      <c r="E212" s="16" t="s">
         <v>909</v>
       </c>
       <c r="F212" s="3" t="s">
@@ -17616,70 +17524,70 @@
         <v>911</v>
       </c>
     </row>
-    <row r="213" ht="13" customHeight="1" spans="1:6">
+    <row r="213" ht="13" customHeight="1" spans="1:7">
       <c r="A213" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B213" s="3">
         <v>1205</v>
       </c>
-      <c r="E213" s="7" t="s">
+      <c r="E213" s="14" t="s">
         <v>912</v>
       </c>
-      <c r="F213" s="7"/>
-    </row>
-    <row r="214" s="4" customFormat="1" spans="2:7">
+      <c r="F213" s="14"/>
+    </row>
+    <row r="214" s="3" customFormat="1" spans="1:7">
       <c r="B214" s="3">
         <v>1206</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="E214" s="4" t="s">
+      <c r="E214" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="F214" s="4" t="s">
+      <c r="F214" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="G214" s="4" t="s">
+      <c r="G214" s="3" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="215" s="4" customFormat="1" spans="2:7">
+    <row r="215" s="3" customFormat="1" spans="1:7">
       <c r="B215" s="3">
         <v>1207</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="E215" s="4" t="s">
+      <c r="E215" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="F215" s="4" t="s">
+      <c r="F215" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="G215" s="4" t="s">
+      <c r="G215" s="3" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="216" s="4" customFormat="1" spans="2:7">
+    <row r="216" s="3" customFormat="1" spans="1:7">
       <c r="B216" s="3">
         <v>1208</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="E216" s="4" t="s">
+      <c r="E216" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="F216" s="4" t="s">
+      <c r="F216" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="G216" s="4" t="s">
+      <c r="G216" s="3" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="217" spans="2:7">
+    <row r="217" spans="1:7">
       <c r="B217" s="3">
         <v>1209</v>
       </c>
@@ -17696,7 +17604,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="218" spans="2:7">
+    <row r="218" spans="1:7">
       <c r="B218" s="3">
         <v>1210</v>
       </c>
@@ -17713,7 +17621,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="219" spans="2:7">
+    <row r="219" spans="1:7">
       <c r="B219" s="3">
         <v>1211</v>
       </c>
@@ -17730,7 +17638,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="220" spans="2:7">
+    <row r="220" spans="1:7">
       <c r="B220" s="3">
         <v>1212</v>
       </c>
@@ -17747,7 +17655,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="221" spans="2:7">
+    <row r="221" spans="1:7">
       <c r="B221" s="3">
         <v>1213</v>
       </c>
@@ -17764,7 +17672,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="222" spans="2:7">
+    <row r="222" spans="1:7">
       <c r="B222" s="3">
         <v>1214</v>
       </c>
@@ -17781,7 +17689,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="223" spans="2:7">
+    <row r="223" spans="1:7">
       <c r="B223" s="3">
         <v>1215</v>
       </c>
@@ -17798,7 +17706,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="224" spans="2:7">
+    <row r="224" spans="1:7">
       <c r="B224" s="3">
         <v>1216</v>
       </c>
@@ -17815,19 +17723,19 @@
         <v>929</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:7">
       <c r="A225" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B225" s="3">
         <v>1217</v>
       </c>
-      <c r="E225" s="7" t="s">
+      <c r="E225" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="F225" s="7"/>
-    </row>
-    <row r="226" spans="2:7">
+      <c r="F225" s="14"/>
+    </row>
+    <row r="226" spans="1:7">
       <c r="B226" s="3">
         <v>1218</v>
       </c>
@@ -17837,14 +17745,14 @@
       <c r="E226" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="F226" s="4" t="s">
+      <c r="F226" s="3" t="s">
         <v>946</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="227" spans="2:7">
+    <row r="227" spans="1:7">
       <c r="B227" s="3">
         <v>1219</v>
       </c>
@@ -17854,14 +17762,14 @@
       <c r="E227" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="F227" s="4" t="s">
+      <c r="F227" s="3" t="s">
         <v>950</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="228" spans="2:7">
+    <row r="228" spans="1:7">
       <c r="B228" s="3">
         <v>1220</v>
       </c>
@@ -17871,14 +17779,14 @@
       <c r="E228" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F228" s="4" t="s">
+      <c r="F228" s="3" t="s">
         <v>954</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="229" spans="2:7">
+    <row r="229" spans="1:7">
       <c r="B229" s="3">
         <v>1221</v>
       </c>
@@ -17888,14 +17796,14 @@
       <c r="E229" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="F229" s="4" t="s">
+      <c r="F229" s="3" t="s">
         <v>958</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="230" spans="2:7">
+    <row r="230" spans="1:7">
       <c r="B230" s="3">
         <v>1222</v>
       </c>
@@ -17912,7 +17820,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="231" spans="2:7">
+    <row r="231" spans="1:7">
       <c r="B231" s="3">
         <v>1223</v>
       </c>
@@ -17929,7 +17837,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="232" spans="2:7">
+    <row r="232" spans="1:7">
       <c r="B232" s="3">
         <v>1224</v>
       </c>
@@ -17946,7 +17854,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="233" spans="2:7">
+    <row r="233" spans="1:7">
       <c r="B233" s="3">
         <v>1225</v>
       </c>
@@ -17963,7 +17871,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="234" spans="2:7">
+    <row r="234" spans="1:7">
       <c r="B234" s="3">
         <v>1226</v>
       </c>
@@ -17980,7 +17888,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="235" spans="2:7">
+    <row r="235" spans="1:7">
       <c r="B235" s="3">
         <v>1227</v>
       </c>
@@ -17997,7 +17905,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="236" spans="2:7">
+    <row r="236" spans="1:7">
       <c r="B236" s="3">
         <v>1228</v>
       </c>
@@ -18014,7 +17922,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="237" spans="2:7">
+    <row r="237" spans="1:7">
       <c r="B237" s="3">
         <v>1229</v>
       </c>
@@ -18031,7 +17939,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="238" spans="2:7">
+    <row r="238" spans="1:7">
       <c r="B238" s="3">
         <v>1230</v>
       </c>
@@ -18048,7 +17956,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="239" spans="2:7">
+    <row r="239" spans="1:7">
       <c r="B239" s="3">
         <v>1231</v>
       </c>
@@ -18065,7 +17973,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="240" spans="2:7">
+    <row r="240" spans="1:7">
       <c r="B240" s="3">
         <v>1232</v>
       </c>
@@ -18626,7 +18534,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="273" s="3" customFormat="1" spans="2:7">
+    <row r="273" s="3" customFormat="1" spans="1:9">
       <c r="B273" s="3">
         <v>1265</v>
       </c>
@@ -18643,7 +18551,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="274" s="3" customFormat="1" spans="2:7">
+    <row r="274" s="3" customFormat="1" spans="1:9">
       <c r="B274" s="3">
         <v>1266</v>
       </c>
@@ -18660,7 +18568,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="275" s="3" customFormat="1" spans="2:7">
+    <row r="275" s="3" customFormat="1" spans="1:9">
       <c r="B275" s="3">
         <v>1267</v>
       </c>
@@ -18677,7 +18585,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="276" s="3" customFormat="1" spans="2:7">
+    <row r="276" s="3" customFormat="1" spans="1:9">
       <c r="B276" s="3">
         <v>1268</v>
       </c>
@@ -18694,7 +18602,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" s="3" customFormat="1" spans="2:7">
+    <row r="277" s="3" customFormat="1" spans="1:9">
       <c r="B277" s="3">
         <v>1269</v>
       </c>
@@ -18711,14 +18619,14 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="278" s="3" customFormat="1" spans="2:7">
+    <row r="278" s="3" customFormat="1" spans="1:9">
       <c r="B278" s="3">
         <v>1270</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="E278" s="46" t="s">
+      <c r="E278" s="43" t="s">
         <v>1121</v>
       </c>
       <c r="F278" s="3" t="s">
@@ -18728,14 +18636,14 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="279" s="3" customFormat="1" spans="2:7">
+    <row r="279" s="3" customFormat="1" spans="1:9">
       <c r="B279" s="3">
         <v>1271</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="E279" s="46" t="s">
+      <c r="E279" s="43" t="s">
         <v>1124</v>
       </c>
       <c r="F279" s="3" t="s">
@@ -18745,36 +18653,36 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:9">
       <c r="A280" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B280" s="3">
         <v>1272</v>
       </c>
-      <c r="E280" s="7" t="s">
+      <c r="E280" s="14" t="s">
         <v>1126</v>
       </c>
-      <c r="F280" s="7"/>
-    </row>
-    <row r="281" spans="2:7">
+      <c r="F280" s="14"/>
+    </row>
+    <row r="281" spans="1:9">
       <c r="B281" s="3">
         <v>1273</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>1127</v>
       </c>
-      <c r="E281" s="4" t="s">
+      <c r="E281" s="3" t="s">
         <v>1128</v>
       </c>
-      <c r="F281" s="4" t="s">
+      <c r="F281" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G281" s="4" t="s">
+      <c r="G281" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="282" spans="2:9">
+    <row r="282" spans="1:9">
       <c r="B282" s="3">
         <v>1274</v>
       </c>
@@ -18794,7 +18702,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="283" spans="2:7">
+    <row r="283" spans="1:9">
       <c r="B283" s="3">
         <v>1275</v>
       </c>
@@ -18811,19 +18719,19 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:9">
       <c r="A284" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B284" s="3">
         <v>1276</v>
       </c>
-      <c r="E284" s="7" t="s">
+      <c r="E284" s="14" t="s">
         <v>1137</v>
       </c>
-      <c r="F284" s="7"/>
-    </row>
-    <row r="285" spans="2:7">
+      <c r="F284" s="14"/>
+    </row>
+    <row r="285" spans="1:9">
       <c r="B285" s="3">
         <v>1277</v>
       </c>
@@ -18840,7 +18748,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="286" spans="2:7">
+    <row r="286" spans="1:9">
       <c r="B286" s="3">
         <v>1278</v>
       </c>
@@ -18857,7 +18765,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="287" spans="2:7">
+    <row r="287" spans="1:9">
       <c r="B287" s="3">
         <v>1279</v>
       </c>
@@ -18874,7 +18782,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="288" spans="2:7">
+    <row r="288" spans="1:9">
       <c r="B288" s="3">
         <v>1280</v>
       </c>
@@ -18891,7 +18799,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="289" spans="2:7">
+    <row r="289" spans="1:7">
       <c r="B289" s="3">
         <v>1281</v>
       </c>
@@ -18908,7 +18816,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="290" spans="2:7">
+    <row r="290" spans="1:7">
       <c r="B290" s="3">
         <v>1282</v>
       </c>
@@ -18925,7 +18833,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="291" spans="2:7">
+    <row r="291" spans="1:7">
       <c r="B291" s="3">
         <v>1283</v>
       </c>
@@ -18942,7 +18850,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="292" spans="2:7">
+    <row r="292" spans="1:7">
       <c r="B292" s="3">
         <v>1284</v>
       </c>
@@ -18959,7 +18867,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="293" spans="2:7">
+    <row r="293" spans="1:7">
       <c r="B293" s="3">
         <v>1285</v>
       </c>
@@ -18976,7 +18884,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="294" spans="2:7">
+    <row r="294" spans="1:7">
       <c r="B294" s="3">
         <v>1286</v>
       </c>
@@ -18993,19 +18901,19 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:7">
       <c r="A295" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B295" s="3">
         <v>1287</v>
       </c>
-      <c r="E295" s="7" t="s">
+      <c r="E295" s="14" t="s">
         <v>1177</v>
       </c>
-      <c r="F295" s="7"/>
-    </row>
-    <row r="296" spans="2:7">
+      <c r="F295" s="14"/>
+    </row>
+    <row r="296" spans="1:7">
       <c r="B296" s="3">
         <v>1288</v>
       </c>
@@ -19022,7 +18930,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="297" spans="2:7">
+    <row r="297" spans="1:7">
       <c r="B297" s="3">
         <v>1289</v>
       </c>
@@ -19032,14 +18940,14 @@
       <c r="E297" s="3" t="s">
         <v>1183</v>
       </c>
-      <c r="F297" s="4" t="s">
+      <c r="F297" s="3" t="s">
         <v>1184</v>
       </c>
       <c r="G297" s="3" t="s">
         <v>1184</v>
       </c>
     </row>
-    <row r="298" spans="2:7">
+    <row r="298" spans="1:7">
       <c r="B298" s="3">
         <v>1290</v>
       </c>
@@ -19052,14 +18960,14 @@
       <c r="E298" s="3" t="s">
         <v>1187</v>
       </c>
-      <c r="F298" s="4" t="s">
+      <c r="F298" s="3" t="s">
         <v>1188</v>
       </c>
       <c r="G298" s="3" t="s">
         <v>1189</v>
       </c>
     </row>
-    <row r="299" spans="2:7">
+    <row r="299" spans="1:7">
       <c r="B299" s="3">
         <v>1291</v>
       </c>
@@ -19079,7 +18987,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="300" spans="2:7">
+    <row r="300" spans="1:7">
       <c r="B300" s="3">
         <v>1292</v>
       </c>
@@ -19096,7 +19004,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="2:7">
+    <row r="301" spans="1:7">
       <c r="B301" s="3">
         <v>1293</v>
       </c>
@@ -19116,7 +19024,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="302" spans="2:7">
+    <row r="302" spans="1:7">
       <c r="B302" s="3">
         <v>1294</v>
       </c>
@@ -19133,7 +19041,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="303" spans="2:7">
+    <row r="303" spans="1:7">
       <c r="B303" s="3">
         <v>1295</v>
       </c>
@@ -19150,7 +19058,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="304" spans="2:7">
+    <row r="304" spans="1:7">
       <c r="B304" s="3">
         <v>1296</v>
       </c>
@@ -19167,19 +19075,19 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:7">
       <c r="A305" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B305" s="3">
         <v>1297</v>
       </c>
-      <c r="E305" s="7" t="s">
+      <c r="E305" s="14" t="s">
         <v>1209</v>
       </c>
-      <c r="F305" s="7"/>
-    </row>
-    <row r="306" spans="2:7">
+      <c r="F305" s="14"/>
+    </row>
+    <row r="306" spans="1:7">
       <c r="B306" s="3">
         <v>1298</v>
       </c>
@@ -19196,92 +19104,92 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="307" spans="2:7">
+    <row r="307" spans="1:7">
       <c r="B307" s="3">
         <v>1299</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>1214</v>
       </c>
-      <c r="E307" s="18" t="s">
+      <c r="E307" s="17" t="s">
         <v>1215</v>
       </c>
-      <c r="F307" s="19" t="s">
+      <c r="F307" s="17" t="s">
         <v>1216</v>
       </c>
       <c r="G307" s="3" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="308" spans="2:7">
+    <row r="308" spans="1:7">
       <c r="B308" s="3">
         <v>1300</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="E308" s="18" t="s">
+      <c r="E308" s="17" t="s">
         <v>1219</v>
       </c>
-      <c r="F308" s="18" t="s">
+      <c r="F308" s="17" t="s">
         <v>1220</v>
       </c>
       <c r="G308" s="3" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="309" spans="2:7">
+    <row r="309" spans="1:7">
       <c r="B309" s="3">
         <v>1301</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="E309" s="18" t="s">
+      <c r="E309" s="17" t="s">
         <v>1223</v>
       </c>
-      <c r="F309" s="18" t="s">
+      <c r="F309" s="17" t="s">
         <v>1224</v>
       </c>
-      <c r="G309" s="16" t="s">
+      <c r="G309" s="15" t="s">
         <v>1225</v>
       </c>
     </row>
-    <row r="310" spans="2:7">
+    <row r="310" spans="1:7">
       <c r="B310" s="3">
         <v>1302</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="E310" s="18" t="s">
+      <c r="E310" s="17" t="s">
         <v>1227</v>
       </c>
-      <c r="F310" s="18" t="s">
+      <c r="F310" s="17" t="s">
         <v>1228</v>
       </c>
       <c r="G310" s="3" t="s">
         <v>1228</v>
       </c>
     </row>
-    <row r="311" spans="2:7">
+    <row r="311" spans="1:7">
       <c r="B311" s="3">
         <v>1303</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="E311" s="18" t="s">
+      <c r="E311" s="17" t="s">
         <v>1230</v>
       </c>
-      <c r="F311" s="18" t="s">
+      <c r="F311" s="17" t="s">
         <v>1231</v>
       </c>
       <c r="G311" s="3" t="s">
         <v>1231</v>
       </c>
     </row>
-    <row r="312" spans="2:7">
+    <row r="312" spans="1:7">
       <c r="B312" s="3">
         <v>1304</v>
       </c>
@@ -19298,7 +19206,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="313" spans="2:7">
+    <row r="313" spans="1:7">
       <c r="B313" s="3">
         <v>1305</v>
       </c>
@@ -19315,7 +19223,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="314" spans="2:7">
+    <row r="314" spans="1:7">
       <c r="B314" s="3">
         <v>1306</v>
       </c>
@@ -19332,7 +19240,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="315" spans="2:7">
+    <row r="315" spans="1:7">
       <c r="B315" s="3">
         <v>1307</v>
       </c>
@@ -19349,7 +19257,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="316" spans="2:7">
+    <row r="316" spans="1:7">
       <c r="B316" s="3">
         <v>1308</v>
       </c>
@@ -19366,7 +19274,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="317" spans="2:7">
+    <row r="317" spans="1:7">
       <c r="B317" s="3">
         <v>1309</v>
       </c>
@@ -19383,7 +19291,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="318" spans="2:7">
+    <row r="318" spans="1:7">
       <c r="B318" s="3">
         <v>1310</v>
       </c>
@@ -19400,7 +19308,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="319" spans="2:7">
+    <row r="319" spans="1:7">
       <c r="B319" s="3">
         <v>1311</v>
       </c>
@@ -19417,7 +19325,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="320" s="3" customFormat="1" spans="2:7">
+    <row r="320" s="3" customFormat="1" spans="1:7">
       <c r="B320" s="3">
         <v>1312</v>
       </c>
@@ -19434,7 +19342,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="321" s="3" customFormat="1" spans="2:7">
+    <row r="321" s="3" customFormat="1" spans="1:7">
       <c r="B321" s="3">
         <v>1313</v>
       </c>
@@ -19451,7 +19359,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="322" s="3" customFormat="1" spans="2:7">
+    <row r="322" s="3" customFormat="1" spans="1:7">
       <c r="B322" s="3">
         <v>1314</v>
       </c>
@@ -19468,7 +19376,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="323" s="3" customFormat="1" spans="2:7">
+    <row r="323" s="3" customFormat="1" spans="1:7">
       <c r="B323" s="3">
         <v>1315</v>
       </c>
@@ -19485,7 +19393,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="324" s="3" customFormat="1" spans="2:7">
+    <row r="324" s="3" customFormat="1" spans="1:7">
       <c r="B324" s="3">
         <v>1316</v>
       </c>
@@ -19502,7 +19410,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="325" s="3" customFormat="1" spans="2:7">
+    <row r="325" s="3" customFormat="1" spans="1:7">
       <c r="B325" s="3">
         <v>1317</v>
       </c>
@@ -19519,7 +19427,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="326" s="3" customFormat="1" spans="2:7">
+    <row r="326" s="3" customFormat="1" spans="1:7">
       <c r="B326" s="3">
         <v>1318</v>
       </c>
@@ -19536,7 +19444,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="327" s="3" customFormat="1" spans="2:7">
+    <row r="327" s="3" customFormat="1" spans="1:7">
       <c r="B327" s="3">
         <v>1319</v>
       </c>
@@ -19553,7 +19461,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="328" s="3" customFormat="1" spans="2:7">
+    <row r="328" s="3" customFormat="1" spans="1:7">
       <c r="B328" s="3">
         <v>1320</v>
       </c>
@@ -19570,19 +19478,19 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:7">
       <c r="A329" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B329" s="3">
         <v>1321</v>
       </c>
-      <c r="E329" s="7" t="s">
+      <c r="E329" s="14" t="s">
         <v>1283</v>
       </c>
-      <c r="F329" s="7"/>
-    </row>
-    <row r="330" spans="2:7">
+      <c r="F329" s="14"/>
+    </row>
+    <row r="330" spans="1:7">
       <c r="B330" s="3">
         <v>1322</v>
       </c>
@@ -19592,14 +19500,14 @@
       <c r="E330" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="F330" s="4" t="s">
+      <c r="F330" s="3" t="s">
         <v>1286</v>
       </c>
       <c r="G330" s="3" t="s">
         <v>1287</v>
       </c>
     </row>
-    <row r="331" spans="2:7">
+    <row r="331" spans="1:7">
       <c r="B331" s="3">
         <v>1323</v>
       </c>
@@ -19609,26 +19517,26 @@
       <c r="E331" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="F331" s="4" t="s">
+      <c r="F331" s="3" t="s">
         <v>1290</v>
       </c>
       <c r="G331" s="3" t="s">
         <v>1290</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:7">
       <c r="A332" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B332" s="3">
         <v>1324</v>
       </c>
-      <c r="E332" s="7" t="s">
+      <c r="E332" s="14" t="s">
         <v>1291</v>
       </c>
-      <c r="F332" s="7"/>
-    </row>
-    <row r="333" spans="2:7">
+      <c r="F332" s="14"/>
+    </row>
+    <row r="333" spans="1:7">
       <c r="B333" s="3">
         <v>1325</v>
       </c>
@@ -19645,7 +19553,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="334" spans="2:7">
+    <row r="334" spans="1:7">
       <c r="B334" s="3">
         <v>1326</v>
       </c>
@@ -19662,7 +19570,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="335" spans="2:7">
+    <row r="335" spans="1:7">
       <c r="B335" s="3">
         <v>1327</v>
       </c>
@@ -19679,7 +19587,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="336" spans="2:7">
+    <row r="336" spans="1:7">
       <c r="B336" s="3">
         <v>1328</v>
       </c>
@@ -19696,7 +19604,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="337" spans="2:7">
+    <row r="337" spans="1:7">
       <c r="B337" s="3">
         <v>1329</v>
       </c>
@@ -19713,7 +19621,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="338" spans="2:7">
+    <row r="338" spans="1:7">
       <c r="B338" s="3">
         <v>1330</v>
       </c>
@@ -19730,7 +19638,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="339" spans="2:7">
+    <row r="339" spans="1:7">
       <c r="B339" s="3">
         <v>1331</v>
       </c>
@@ -19747,7 +19655,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="340" spans="2:7">
+    <row r="340" spans="1:7">
       <c r="B340" s="3">
         <v>1332</v>
       </c>
@@ -19764,7 +19672,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="341" spans="2:7">
+    <row r="341" spans="1:7">
       <c r="B341" s="3">
         <v>1333</v>
       </c>
@@ -19781,7 +19689,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="342" spans="2:7">
+    <row r="342" spans="1:7">
       <c r="B342" s="3">
         <v>1334</v>
       </c>
@@ -19798,7 +19706,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="343" spans="2:7">
+    <row r="343" spans="1:7">
       <c r="B343" s="3">
         <v>1335</v>
       </c>
@@ -19815,7 +19723,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="344" spans="2:7">
+    <row r="344" spans="1:7">
       <c r="B344" s="3">
         <v>1336</v>
       </c>
@@ -19832,25 +19740,25 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:7">
       <c r="A345" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B345" s="3">
         <v>1337</v>
       </c>
-      <c r="E345" s="7" t="s">
+      <c r="E345" s="14" t="s">
         <v>1330</v>
       </c>
     </row>
-    <row r="346" spans="2:7">
+    <row r="346" spans="1:7">
       <c r="B346" s="3">
         <v>1338</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>1331</v>
       </c>
-      <c r="E346" s="17" t="s">
+      <c r="E346" s="16" t="s">
         <v>1332</v>
       </c>
       <c r="F346" s="3" t="s">
@@ -19860,14 +19768,14 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="347" spans="2:7">
+    <row r="347" spans="1:7">
       <c r="B347" s="3">
         <v>1339</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>1335</v>
       </c>
-      <c r="E347" s="17" t="s">
+      <c r="E347" s="16" t="s">
         <v>1336</v>
       </c>
       <c r="F347" s="3" t="s">
@@ -19877,14 +19785,14 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="348" spans="2:7">
+    <row r="348" spans="1:7">
       <c r="B348" s="3">
         <v>1340</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>1339</v>
       </c>
-      <c r="E348" s="17" t="s">
+      <c r="E348" s="16" t="s">
         <v>1340</v>
       </c>
       <c r="F348" s="3" t="s">
@@ -19894,19 +19802,19 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:7">
       <c r="A349" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B349" s="3">
         <v>1341</v>
       </c>
-      <c r="E349" s="7" t="s">
+      <c r="E349" s="14" t="s">
         <v>1343</v>
       </c>
-      <c r="F349" s="7"/>
-    </row>
-    <row r="350" s="3" customFormat="1" spans="2:7">
+      <c r="F349" s="14"/>
+    </row>
+    <row r="350" s="3" customFormat="1" spans="1:7">
       <c r="B350" s="3">
         <v>1342</v>
       </c>
@@ -19916,14 +19824,14 @@
       <c r="E350" s="3" t="s">
         <v>1345</v>
       </c>
-      <c r="F350" s="16" t="s">
+      <c r="F350" s="15" t="s">
         <v>1346</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="351" spans="2:7">
+    <row r="351" spans="1:7">
       <c r="B351" s="3">
         <v>1343</v>
       </c>
@@ -19933,14 +19841,14 @@
       <c r="E351" s="3" t="s">
         <v>1349</v>
       </c>
-      <c r="F351" s="16" t="s">
+      <c r="F351" s="15" t="s">
         <v>1350</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="352" spans="2:7">
+    <row r="352" spans="1:7">
       <c r="B352" s="3">
         <v>1344</v>
       </c>
@@ -19950,7 +19858,7 @@
       <c r="E352" s="3" t="s">
         <v>1353</v>
       </c>
-      <c r="F352" s="16" t="s">
+      <c r="F352" s="15" t="s">
         <v>1354</v>
       </c>
       <c r="G352" s="3" t="s">
@@ -19967,7 +19875,7 @@
       <c r="E353" s="3" t="s">
         <v>1357</v>
       </c>
-      <c r="F353" s="16" t="s">
+      <c r="F353" s="15" t="s">
         <v>1358</v>
       </c>
       <c r="G353" s="3" t="s">
@@ -19984,7 +19892,7 @@
       <c r="E354" s="3" t="s">
         <v>1361</v>
       </c>
-      <c r="F354" s="16" t="s">
+      <c r="F354" s="15" t="s">
         <v>1362</v>
       </c>
       <c r="G354" s="3" t="s">
@@ -20001,7 +19909,7 @@
       <c r="E355" s="3" t="s">
         <v>1365</v>
       </c>
-      <c r="F355" s="16" t="s">
+      <c r="F355" s="15" t="s">
         <v>1366</v>
       </c>
       <c r="G355" s="3" t="s">
@@ -20018,7 +19926,7 @@
       <c r="E356" s="3" t="s">
         <v>1369</v>
       </c>
-      <c r="F356" s="16" t="s">
+      <c r="F356" s="15" t="s">
         <v>1370</v>
       </c>
       <c r="G356" s="3" t="s">
@@ -20035,7 +19943,7 @@
       <c r="E357" s="3" t="s">
         <v>1373</v>
       </c>
-      <c r="F357" s="16" t="s">
+      <c r="F357" s="15" t="s">
         <v>1374</v>
       </c>
       <c r="G357" s="3" t="s">
@@ -20052,7 +19960,7 @@
       <c r="E358" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="F358" s="16" t="s">
+      <c r="F358" s="15" t="s">
         <v>1378</v>
       </c>
       <c r="G358" s="3" t="s">
@@ -20069,7 +19977,7 @@
       <c r="E359" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="F359" s="16" t="s">
+      <c r="F359" s="15" t="s">
         <v>1382</v>
       </c>
       <c r="G359" s="3" t="s">
@@ -20086,7 +19994,7 @@
       <c r="E360" s="3" t="s">
         <v>1385</v>
       </c>
-      <c r="F360" s="16" t="s">
+      <c r="F360" s="15" t="s">
         <v>1386</v>
       </c>
       <c r="G360" s="3" t="s">
@@ -20103,7 +20011,7 @@
       <c r="E361" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="F361" s="16" t="s">
+      <c r="F361" s="15" t="s">
         <v>1390</v>
       </c>
       <c r="G361" s="3" t="s">
@@ -20120,7 +20028,7 @@
       <c r="E362" s="3" t="s">
         <v>1393</v>
       </c>
-      <c r="F362" s="16" t="s">
+      <c r="F362" s="15" t="s">
         <v>1394</v>
       </c>
       <c r="G362" s="3" t="s">
@@ -20137,7 +20045,7 @@
       <c r="E363" s="3" t="s">
         <v>1397</v>
       </c>
-      <c r="F363" s="16" t="s">
+      <c r="F363" s="15" t="s">
         <v>1398</v>
       </c>
       <c r="G363" s="3" t="s">
@@ -20154,7 +20062,7 @@
       <c r="E364" s="3" t="s">
         <v>1401</v>
       </c>
-      <c r="F364" s="16" t="s">
+      <c r="F364" s="15" t="s">
         <v>1402</v>
       </c>
       <c r="G364" s="3" t="s">
@@ -20171,7 +20079,7 @@
       <c r="E365" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="F365" s="16" t="s">
+      <c r="F365" s="15" t="s">
         <v>1406</v>
       </c>
       <c r="G365" s="3" t="s">
@@ -20188,7 +20096,7 @@
       <c r="E366" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="F366" s="16" t="s">
+      <c r="F366" s="15" t="s">
         <v>1410</v>
       </c>
       <c r="G366" s="3" t="s">
@@ -20205,7 +20113,7 @@
       <c r="E367" s="3" t="s">
         <v>1413</v>
       </c>
-      <c r="F367" s="16" t="s">
+      <c r="F367" s="15" t="s">
         <v>1414</v>
       </c>
       <c r="G367" s="3" t="s">
@@ -20222,14 +20130,14 @@
       <c r="E368" s="3" t="s">
         <v>1417</v>
       </c>
-      <c r="F368" s="16" t="s">
+      <c r="F368" s="15" t="s">
         <v>1418</v>
       </c>
       <c r="G368" s="3" t="s">
         <v>1419</v>
       </c>
     </row>
-    <row r="369" spans="2:7">
+    <row r="369" spans="1:7">
       <c r="B369" s="3">
         <v>1361</v>
       </c>
@@ -20239,14 +20147,14 @@
       <c r="E369" s="3" t="s">
         <v>1421</v>
       </c>
-      <c r="F369" s="16" t="s">
+      <c r="F369" s="15" t="s">
         <v>1422</v>
       </c>
       <c r="G369" s="3" t="s">
         <v>1423</v>
       </c>
     </row>
-    <row r="370" spans="2:7">
+    <row r="370" spans="1:7">
       <c r="B370" s="3">
         <v>1362</v>
       </c>
@@ -20263,7 +20171,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="371" spans="2:7">
+    <row r="371" spans="1:7">
       <c r="B371" s="3">
         <v>1363</v>
       </c>
@@ -20280,7 +20188,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="372" spans="2:7">
+    <row r="372" spans="1:7">
       <c r="B372" s="3">
         <v>1364</v>
       </c>
@@ -20297,7 +20205,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="373" spans="2:7">
+    <row r="373" spans="1:7">
       <c r="B373" s="3">
         <v>1365</v>
       </c>
@@ -20307,14 +20215,14 @@
       <c r="E373" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="F373" s="16" t="s">
+      <c r="F373" s="15" t="s">
         <v>1346</v>
       </c>
       <c r="G373" s="3" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="374" spans="2:7">
+    <row r="374" spans="1:7">
       <c r="B374" s="3">
         <v>1366</v>
       </c>
@@ -20324,14 +20232,14 @@
       <c r="E374" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="F374" s="16" t="s">
+      <c r="F374" s="15" t="s">
         <v>1438</v>
       </c>
       <c r="G374" s="3" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="375" spans="2:7">
+    <row r="375" spans="1:7">
       <c r="B375" s="3">
         <v>1367</v>
       </c>
@@ -20341,14 +20249,14 @@
       <c r="E375" s="3" t="s">
         <v>1441</v>
       </c>
-      <c r="F375" s="16" t="s">
+      <c r="F375" s="15" t="s">
         <v>1442</v>
       </c>
       <c r="G375" s="3" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="376" spans="2:7">
+    <row r="376" spans="1:7">
       <c r="B376" s="3">
         <v>1368</v>
       </c>
@@ -20358,14 +20266,14 @@
       <c r="E376" s="3" t="s">
         <v>1445</v>
       </c>
-      <c r="F376" s="16" t="s">
+      <c r="F376" s="15" t="s">
         <v>1446</v>
       </c>
       <c r="G376" s="3" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="377" spans="2:7">
+    <row r="377" spans="1:7">
       <c r="B377" s="3">
         <v>1369</v>
       </c>
@@ -20375,14 +20283,14 @@
       <c r="E377" s="3" t="s">
         <v>1449</v>
       </c>
-      <c r="F377" s="16" t="s">
+      <c r="F377" s="15" t="s">
         <v>1450</v>
       </c>
       <c r="G377" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="378" spans="2:7">
+    <row r="378" spans="1:7">
       <c r="B378" s="3">
         <v>1370</v>
       </c>
@@ -20392,14 +20300,14 @@
       <c r="E378" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="F378" s="16" t="s">
+      <c r="F378" s="15" t="s">
         <v>1453</v>
       </c>
       <c r="G378" s="3" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="379" spans="2:7">
+    <row r="379" spans="1:7">
       <c r="B379" s="3">
         <v>1371</v>
       </c>
@@ -20409,14 +20317,14 @@
       <c r="E379" s="3" t="s">
         <v>1456</v>
       </c>
-      <c r="F379" s="16" t="s">
+      <c r="F379" s="15" t="s">
         <v>1457</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="380" spans="2:7">
+    <row r="380" spans="1:7">
       <c r="B380" s="3">
         <v>1372</v>
       </c>
@@ -20426,14 +20334,14 @@
       <c r="E380" s="3" t="s">
         <v>1460</v>
       </c>
-      <c r="F380" s="16" t="s">
+      <c r="F380" s="15" t="s">
         <v>1461</v>
       </c>
       <c r="G380" s="3" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="381" ht="27" spans="2:7">
+    <row r="381" ht="27" spans="1:7">
       <c r="B381" s="3">
         <v>1373</v>
       </c>
@@ -20443,26 +20351,26 @@
       <c r="E381" s="3" t="s">
         <v>1464</v>
       </c>
-      <c r="F381" s="16" t="s">
+      <c r="F381" s="15" t="s">
         <v>1465</v>
       </c>
       <c r="G381" s="3" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:7">
       <c r="A382" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B382" s="3">
         <v>1374</v>
       </c>
-      <c r="E382" s="7" t="s">
+      <c r="E382" s="14" t="s">
         <v>1467</v>
       </c>
-      <c r="F382" s="7"/>
-    </row>
-    <row r="383" spans="2:7">
+      <c r="F382" s="14"/>
+    </row>
+    <row r="383" spans="1:7">
       <c r="B383" s="3">
         <v>1375</v>
       </c>
@@ -20479,7 +20387,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="384" spans="2:7">
+    <row r="384" spans="1:7">
       <c r="B384" s="3">
         <v>1376</v>
       </c>
@@ -20496,18 +20404,18 @@
         <v>468</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:7">
       <c r="A385" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B385" s="3">
         <v>1377</v>
       </c>
-      <c r="E385" s="7" t="s">
+      <c r="E385" s="14" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="386" spans="2:7">
+    <row r="386" spans="1:7">
       <c r="B386" s="3">
         <v>1378</v>
       </c>
@@ -20524,7 +20432,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="387" spans="2:7">
+    <row r="387" spans="1:7">
       <c r="B387" s="3">
         <v>1379</v>
       </c>
@@ -20541,7 +20449,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="388" spans="2:7">
+    <row r="388" spans="1:7">
       <c r="B388" s="3">
         <v>1380</v>
       </c>
@@ -20558,7 +20466,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="389" spans="2:7">
+    <row r="389" spans="1:7">
       <c r="B389" s="3">
         <v>1381</v>
       </c>
@@ -20575,7 +20483,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="390" spans="2:7">
+    <row r="390" spans="1:7">
       <c r="B390" s="3">
         <v>1382</v>
       </c>
@@ -20592,7 +20500,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="391" spans="2:7">
+    <row r="391" spans="1:7">
       <c r="B391" s="3">
         <v>1383</v>
       </c>
@@ -20609,7 +20517,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="392" spans="2:7">
+    <row r="392" spans="1:7">
       <c r="B392" s="3">
         <v>1384</v>
       </c>
@@ -20626,7 +20534,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="393" spans="2:7">
+    <row r="393" spans="1:7">
       <c r="B393" s="3">
         <v>1385</v>
       </c>
@@ -20643,7 +20551,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="394" spans="2:7">
+    <row r="394" spans="1:7">
       <c r="B394" s="3">
         <v>1386</v>
       </c>
@@ -20660,7 +20568,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="395" spans="2:7">
+    <row r="395" spans="1:7">
       <c r="B395" s="3">
         <v>1387</v>
       </c>
@@ -20677,7 +20585,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="396" spans="2:7">
+    <row r="396" spans="1:7">
       <c r="B396" s="3">
         <v>1388</v>
       </c>
@@ -20694,7 +20602,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="397" spans="2:7">
+    <row r="397" spans="1:7">
       <c r="B397" s="3">
         <v>1389</v>
       </c>
@@ -20711,7 +20619,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="398" spans="2:7">
+    <row r="398" spans="1:7">
       <c r="B398" s="3">
         <v>1390</v>
       </c>
@@ -20728,7 +20636,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="399" spans="2:7">
+    <row r="399" spans="1:7">
       <c r="B399" s="3">
         <v>1391</v>
       </c>
@@ -20745,15 +20653,15 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="400" spans="2:5">
+    <row r="400" spans="1:7">
       <c r="B400" s="3">
         <v>1392</v>
       </c>
-      <c r="E400" s="7" t="s">
+      <c r="E400" s="14" t="s">
         <v>1520</v>
       </c>
     </row>
-    <row r="401" spans="2:7">
+    <row r="401" spans="1:7">
       <c r="B401" s="3">
         <v>1393</v>
       </c>
@@ -20770,7 +20678,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="402" spans="2:7">
+    <row r="402" spans="1:7">
       <c r="B402" s="3">
         <v>1394</v>
       </c>
@@ -20787,121 +20695,121 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:7">
       <c r="A403" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B403" s="3">
         <v>1395</v>
       </c>
-      <c r="E403" s="7" t="s">
+      <c r="E403" s="14" t="s">
         <v>1529</v>
       </c>
-      <c r="F403" s="7"/>
-    </row>
-    <row r="404" spans="2:7">
+      <c r="F403" s="14"/>
+    </row>
+    <row r="404" spans="1:7">
       <c r="B404" s="3">
         <v>1396</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>1530</v>
       </c>
-      <c r="E404" s="17" t="s">
+      <c r="E404" s="16" t="s">
         <v>1531</v>
       </c>
-      <c r="F404" s="17" t="s">
+      <c r="F404" s="16" t="s">
         <v>1532</v>
       </c>
       <c r="G404" s="3" t="s">
         <v>1533</v>
       </c>
     </row>
-    <row r="405" spans="2:7">
+    <row r="405" spans="1:7">
       <c r="B405" s="3">
         <v>1397</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="E405" s="17" t="s">
+      <c r="E405" s="16" t="s">
         <v>1535</v>
       </c>
-      <c r="F405" s="17" t="s">
+      <c r="F405" s="16" t="s">
         <v>1536</v>
       </c>
       <c r="G405" s="3" t="s">
         <v>1537</v>
       </c>
     </row>
-    <row r="406" spans="2:7">
+    <row r="406" spans="1:7">
       <c r="B406" s="3">
         <v>1398</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>1538</v>
       </c>
-      <c r="E406" s="17" t="s">
+      <c r="E406" s="16" t="s">
         <v>1539</v>
       </c>
-      <c r="F406" s="17" t="s">
+      <c r="F406" s="16" t="s">
         <v>1540</v>
       </c>
       <c r="G406" s="3" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="407" spans="2:7">
+    <row r="407" spans="1:7">
       <c r="B407" s="3">
         <v>1399</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>1542</v>
       </c>
-      <c r="E407" s="17" t="s">
+      <c r="E407" s="16" t="s">
         <v>1543</v>
       </c>
-      <c r="F407" s="17" t="s">
+      <c r="F407" s="16" t="s">
         <v>1544</v>
       </c>
       <c r="G407" s="3" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="408" spans="2:7">
+    <row r="408" spans="1:7">
       <c r="B408" s="3">
         <v>1400</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="E408" s="17" t="s">
+      <c r="E408" s="16" t="s">
         <v>1547</v>
       </c>
-      <c r="F408" s="17" t="s">
+      <c r="F408" s="16" t="s">
         <v>1548</v>
       </c>
       <c r="G408" s="3" t="s">
         <v>1549</v>
       </c>
     </row>
-    <row r="409" spans="2:7">
+    <row r="409" spans="1:7">
       <c r="B409" s="3">
         <v>1401</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>1550</v>
       </c>
-      <c r="E409" s="17" t="s">
+      <c r="E409" s="16" t="s">
         <v>1551</v>
       </c>
-      <c r="F409" s="17" t="s">
+      <c r="F409" s="16" t="s">
         <v>1552</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="410" spans="2:7">
+    <row r="410" spans="1:7">
       <c r="B410" s="3">
         <v>1402</v>
       </c>
@@ -20918,7 +20826,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="411" spans="2:7">
+    <row r="411" spans="1:7">
       <c r="B411" s="3">
         <v>1403</v>
       </c>
@@ -20935,7 +20843,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="412" spans="2:7">
+    <row r="412" spans="1:7">
       <c r="B412" s="3">
         <v>1404</v>
       </c>
@@ -20952,7 +20860,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="413" spans="2:7">
+    <row r="413" spans="1:7">
       <c r="B413" s="3">
         <v>1405</v>
       </c>
@@ -20969,7 +20877,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="414" spans="2:7">
+    <row r="414" spans="1:7">
       <c r="B414" s="3">
         <v>1406</v>
       </c>
@@ -20986,7 +20894,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="415" spans="2:7">
+    <row r="415" spans="1:7">
       <c r="B415" s="3">
         <v>1407</v>
       </c>
@@ -21003,7 +20911,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="416" spans="2:7">
+    <row r="416" spans="1:7">
       <c r="B416" s="3">
         <v>1408</v>
       </c>
@@ -21013,26 +20921,26 @@
       <c r="E416" s="3" t="s">
         <v>1578</v>
       </c>
-      <c r="F416" s="16" t="s">
+      <c r="F416" s="15" t="s">
         <v>1579</v>
       </c>
       <c r="G416" s="3" t="s">
         <v>1580</v>
       </c>
     </row>
-    <row r="417" spans="1:6">
+    <row r="417" spans="1:7">
       <c r="A417" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B417" s="3">
         <v>1409</v>
       </c>
-      <c r="E417" s="7" t="s">
+      <c r="E417" s="14" t="s">
         <v>1581</v>
       </c>
-      <c r="F417" s="16"/>
-    </row>
-    <row r="418" spans="2:7">
+      <c r="F417" s="15"/>
+    </row>
+    <row r="418" spans="1:7">
       <c r="B418" s="3">
         <v>1410</v>
       </c>
@@ -21042,14 +20950,14 @@
       <c r="E418" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="F418" s="16" t="s">
+      <c r="F418" s="15" t="s">
         <v>1584</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>1585</v>
       </c>
     </row>
-    <row r="419" spans="2:7">
+    <row r="419" spans="1:7">
       <c r="B419" s="3">
         <v>1411</v>
       </c>
@@ -21059,14 +20967,14 @@
       <c r="E419" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="F419" s="16" t="s">
+      <c r="F419" s="15" t="s">
         <v>1588</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>1589</v>
       </c>
     </row>
-    <row r="420" spans="2:7">
+    <row r="420" spans="1:7">
       <c r="B420" s="3">
         <v>1412</v>
       </c>
@@ -21076,14 +20984,14 @@
       <c r="E420" s="3" t="s">
         <v>1591</v>
       </c>
-      <c r="F420" s="16" t="s">
+      <c r="F420" s="15" t="s">
         <v>1592</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>1593</v>
       </c>
     </row>
-    <row r="421" spans="2:7">
+    <row r="421" spans="1:7">
       <c r="B421" s="3">
         <v>1413</v>
       </c>
@@ -21093,26 +21001,26 @@
       <c r="E421" s="3" t="s">
         <v>1595</v>
       </c>
-      <c r="F421" s="16" t="s">
+      <c r="F421" s="15" t="s">
         <v>1596</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="422" spans="1:6">
+    <row r="422" spans="1:7">
       <c r="A422" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B422" s="3">
         <v>1414</v>
       </c>
-      <c r="E422" s="7" t="s">
+      <c r="E422" s="14" t="s">
         <v>1598</v>
       </c>
-      <c r="F422" s="7"/>
-    </row>
-    <row r="423" spans="2:7">
+      <c r="F422" s="14"/>
+    </row>
+    <row r="423" spans="1:7">
       <c r="B423" s="3">
         <v>1415</v>
       </c>
@@ -21129,7 +21037,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="424" spans="2:7">
+    <row r="424" spans="1:7">
       <c r="B424" s="3">
         <v>1416</v>
       </c>
@@ -21146,7 +21054,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="425" spans="2:7">
+    <row r="425" spans="1:7">
       <c r="B425" s="3">
         <v>1417</v>
       </c>
@@ -21163,7 +21071,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="426" spans="2:7">
+    <row r="426" spans="1:7">
       <c r="B426" s="3">
         <v>1418</v>
       </c>
@@ -21180,7 +21088,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="427" spans="2:7">
+    <row r="427" spans="1:7">
       <c r="B427" s="3">
         <v>1419</v>
       </c>
@@ -21197,7 +21105,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="428" spans="2:7">
+    <row r="428" spans="1:7">
       <c r="B428" s="3">
         <v>1420</v>
       </c>
@@ -21214,7 +21122,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="429" spans="2:7">
+    <row r="429" spans="1:7">
       <c r="B429" s="3">
         <v>1421</v>
       </c>
@@ -21231,7 +21139,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="430" spans="2:7">
+    <row r="430" spans="1:7">
       <c r="B430" s="3">
         <v>1422</v>
       </c>
@@ -21248,7 +21156,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="431" spans="2:7">
+    <row r="431" spans="1:7">
       <c r="B431" s="3">
         <v>1423</v>
       </c>
@@ -21265,7 +21173,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="432" spans="2:7">
+    <row r="432" spans="1:7">
       <c r="B432" s="3">
         <v>1424</v>
       </c>
@@ -21554,7 +21462,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="449" spans="2:7">
+    <row r="449" spans="1:7">
       <c r="B449" s="3">
         <v>1441</v>
       </c>
@@ -21571,7 +21479,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="450" spans="2:7">
+    <row r="450" spans="1:7">
       <c r="B450" s="3">
         <v>1442</v>
       </c>
@@ -21588,7 +21496,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="451" spans="2:7">
+    <row r="451" spans="1:7">
       <c r="B451" s="3">
         <v>1443</v>
       </c>
@@ -21605,7 +21513,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="452" spans="2:7">
+    <row r="452" spans="1:7">
       <c r="B452" s="3">
         <v>1444</v>
       </c>
@@ -21622,7 +21530,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="453" spans="2:7">
+    <row r="453" spans="1:7">
       <c r="B453" s="3">
         <v>1445</v>
       </c>
@@ -21639,7 +21547,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="454" spans="2:7">
+    <row r="454" spans="1:7">
       <c r="B454" s="3">
         <v>1446</v>
       </c>
@@ -21656,7 +21564,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="455" spans="2:7">
+    <row r="455" spans="1:7">
       <c r="B455" s="3">
         <v>1447</v>
       </c>
@@ -21673,7 +21581,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="456" spans="2:7">
+    <row r="456" spans="1:7">
       <c r="B456" s="3">
         <v>1448</v>
       </c>
@@ -21690,7 +21598,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="457" spans="2:7">
+    <row r="457" spans="1:7">
       <c r="B457" s="3">
         <v>1449</v>
       </c>
@@ -21707,18 +21615,18 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:7">
       <c r="A458" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B458" s="3">
         <v>1450</v>
       </c>
-      <c r="E458" s="7" t="s">
+      <c r="E458" s="14" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="459" spans="2:7">
+    <row r="459" spans="1:7">
       <c r="B459" s="3">
         <v>1451</v>
       </c>
@@ -21735,7 +21643,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="460" spans="2:7">
+    <row r="460" spans="1:7">
       <c r="B460" s="3">
         <v>1452</v>
       </c>
@@ -21752,7 +21660,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="461" spans="2:7">
+    <row r="461" spans="1:7">
       <c r="B461" s="3">
         <v>1453</v>
       </c>
@@ -21769,7 +21677,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="462" spans="2:7">
+    <row r="462" spans="1:7">
       <c r="B462" s="3">
         <v>1454</v>
       </c>
@@ -21786,7 +21694,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="463" spans="2:7">
+    <row r="463" spans="1:7">
       <c r="B463" s="3">
         <v>1455</v>
       </c>
@@ -21803,7 +21711,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="464" spans="2:7">
+    <row r="464" spans="1:7">
       <c r="B464" s="3">
         <v>1456</v>
       </c>
@@ -22007,11 +21915,11 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="476" spans="2:5">
+    <row r="476" spans="2:7">
       <c r="B476" s="3">
         <v>1468</v>
       </c>
-      <c r="E476" s="7" t="s">
+      <c r="E476" s="14" t="s">
         <v>237</v>
       </c>
     </row>
